--- a/examples/BOUV.OL/BOUV.OL_model.xlsx
+++ b/examples/BOUV.OL/BOUV.OL_model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/425ed27e3db279b7/Desktop/Private prosjekter/equity-research-engine/output/BOUV.OL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F7B04C1CD46E6C4B85F64DCCA811E987BFD6CC6E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_85A16193074F57B90237A96B42DE2B058110B635" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,12 +42,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="280">
   <si>
     <t>Bouvet ASA (BOUV.OL) – valuation model</t>
   </si>
   <si>
-    <t>Generated by Equity Research Engine on 2026-09-21</t>
+    <t>Generated by Equity Research Engine on 2026-09-23</t>
   </si>
   <si>
     <t>Share price (NOK)</t>
@@ -140,54 +140,69 @@
     <t>Net debt</t>
   </si>
   <si>
-    <t>Latest balance sheet (ex leases)</t>
+    <t>Balance sheet 30.06.2026 (ex leases)</t>
   </si>
   <si>
     <t>Minority interest</t>
   </si>
   <si>
+    <t>Balance sheet 30.06.2026</t>
+  </si>
+  <si>
+    <t>Tax rate</t>
+  </si>
+  <si>
+    <t>config</t>
+  </si>
+  <si>
+    <t>Config</t>
+  </si>
+  <si>
+    <t>Risk-free rate</t>
+  </si>
+  <si>
+    <t>Equity risk premium</t>
+  </si>
+  <si>
+    <t>Beta (adjusted)</t>
+  </si>
+  <si>
+    <t>Yahoo Finance (5y monthly); regression vs OSEBX rejected (R2=0.01 &lt; 0.10), Blume-adjusted</t>
+  </si>
+  <si>
+    <t>Size premium</t>
+  </si>
+  <si>
+    <t>size premium 1.50% (market cap USD 0.5bn)</t>
+  </si>
+  <si>
+    <t>Cost of debt (pre-tax)</t>
+  </si>
+  <si>
+    <t>risk-free + 200bp</t>
+  </si>
+  <si>
+    <t>Gross debt for WACC weights</t>
+  </si>
+  <si>
     <t>Latest balance sheet</t>
   </si>
   <si>
-    <t>Tax rate</t>
-  </si>
-  <si>
-    <t>config</t>
-  </si>
-  <si>
-    <t>Config</t>
-  </si>
-  <si>
-    <t>Risk-free rate</t>
-  </si>
-  <si>
-    <t>Equity risk premium</t>
-  </si>
-  <si>
-    <t>Beta (adjusted)</t>
-  </si>
-  <si>
-    <t>Yahoo Finance (5y monthly); regression vs OSEBX rejected (R2=0.01 &lt; 0.10), Blume-adjusted</t>
-  </si>
-  <si>
-    <t>Size premium</t>
-  </si>
-  <si>
-    <t>size premium 1.50% (market cap USD 0.5bn)</t>
-  </si>
-  <si>
-    <t>Cost of debt (pre-tax)</t>
-  </si>
-  <si>
-    <t>risk-free + 200bp</t>
-  </si>
-  <si>
-    <t>Gross debt for WACC weights</t>
-  </si>
-  <si>
     <t>Mid-year convention (1 = yes)</t>
   </si>
   <si>
+    <t>Years from FY-end to valuation date</t>
+  </si>
+  <si>
+    <t>Valuation date 23.09.2026; last fiscal year-end 31.12.2025</t>
+  </si>
+  <si>
+    <t>Years from FY-end to balance sheet</t>
+  </si>
+  <si>
+    <t>Net debt as at 30.06.2026: year-1 cash flow before that date is already in net debt</t>
+  </si>
+  <si>
     <t>Terminal method (1 = value driver)</t>
   </si>
   <si>
@@ -203,7 +218,7 @@
     <t>Expected dividend per share (NOK)</t>
   </si>
   <si>
-    <t>Last year's cash dividend per share</t>
+    <t>Indicated annual dividend (Yahoo Finance)</t>
   </si>
   <si>
     <t>Roll-forward months</t>
@@ -407,6 +422,21 @@
     <t>Weight of debt</t>
   </si>
   <si>
+    <t>Cross-check: bottom-up beta from the peer group (Hamada, tax at the corporate rate)</t>
+  </si>
+  <si>
+    <t>Median unlevered peer beta</t>
+  </si>
+  <si>
+    <t>Relevered at the target's D/E of 0.00</t>
+  </si>
+  <si>
+    <t>Blume-adjusted (compare with B6)</t>
+  </si>
+  <si>
+    <t>Peers with a usable beta</t>
+  </si>
+  <si>
     <t>Bouvet ASA – DCF valuation (NOKm)</t>
   </si>
   <si>
@@ -416,13 +446,13 @@
     <t>Year</t>
   </si>
   <si>
-    <t>Discount period (years)</t>
+    <t>Discount period (years from valuation date)</t>
   </si>
   <si>
     <t>Discount factor</t>
   </si>
   <si>
-    <t>PV of FCF</t>
+    <t>PV of FCF (year 1: after the balance-sheet date)</t>
   </si>
   <si>
     <t>Sum of PV of FCF</t>
@@ -533,7 +563,7 @@
     <t>Peer multiples</t>
   </si>
   <si>
-    <t>Multiples computed from last reported fiscal year; EV on the same lease basis as the target company.</t>
+    <t>LTM figures where the quarters are reported (else the last fiscal year); EV = market cap today + latest net debt, same lease basis as the target company; P/E on trailing twelve-month EPS.</t>
   </si>
   <si>
     <t>Company</t>
@@ -566,7 +596,34 @@
     <t>P/E</t>
   </si>
   <si>
-    <t>P/E (fwd)</t>
+    <t>P/E (NTM)</t>
+  </si>
+  <si>
+    <t>EV/Sales (NTM)</t>
+  </si>
+  <si>
+    <t>EV/EBITDA (NTM*)</t>
+  </si>
+  <si>
+    <t>P/E (FY0)</t>
+  </si>
+  <si>
+    <t>P/E (FY1)</t>
+  </si>
+  <si>
+    <t>Growth FY1</t>
+  </si>
+  <si>
+    <t>EPS growth</t>
+  </si>
+  <si>
+    <t>PEG</t>
+  </si>
+  <si>
+    <t>FCF yield</t>
+  </si>
+  <si>
+    <t>Div. yield</t>
   </si>
   <si>
     <t>Knowit</t>
@@ -656,16 +713,55 @@
     <t>Market cap</t>
   </si>
   <si>
-    <t>LTM revenue</t>
-  </si>
-  <si>
-    <t>LTM EBITDA</t>
-  </si>
-  <si>
-    <t>LTM EBIT</t>
-  </si>
-  <si>
-    <t>LTM EPS</t>
+    <t>Revenue (LTM Jun 2026)</t>
+  </si>
+  <si>
+    <t>EBITDA (LTM Jun 2026)</t>
+  </si>
+  <si>
+    <t>EBIT (LTM Jun 2026)</t>
+  </si>
+  <si>
+    <t>EPS, trailing 12 months (NOK)</t>
+  </si>
+  <si>
+    <t>Income figures: sum of the four quarters to Jun 2026. Net debt: balance sheet 30.06.2026. EPS: Yahoo Finance trailing twelve months, the same basis as the peers' P/E. * EV/EBITDA (NTM) = EV over NTM consensus revenue at the LTM margin (no EBITDA consensus on Yahoo).</t>
+  </si>
+  <si>
+    <t>EV/EBITDA regression on the peers above (engine OLS with an intercept; coefficients are inputs, the fitted value is live)</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>Coefficient: expected revenue growth</t>
+  </si>
+  <si>
+    <t>Coefficient: EBITDA margin</t>
+  </si>
+  <si>
+    <t>R²</t>
+  </si>
+  <si>
+    <t>Residual standard deviation (x)</t>
+  </si>
+  <si>
+    <t>Peers in the regression</t>
+  </si>
+  <si>
+    <t>Bouvet expected revenue growth</t>
+  </si>
+  <si>
+    <t>Bouvet EBITDA margin (LTM)</t>
+  </si>
+  <si>
+    <t>Fitted EV/EBITDA</t>
+  </si>
+  <si>
+    <t>R² 0.38: used as a football-field bar (±1 residual standard deviation)</t>
+  </si>
+  <si>
+    <t>Regression-implied value per share (NOK)</t>
   </si>
   <si>
     <t>Valuation summary</t>
@@ -699,6 +795,9 @@
   </si>
   <si>
     <t>P/E (peer 25th–75th pct)</t>
+  </si>
+  <si>
+    <t>EV/EBITDA regression (growth, margin ±1σ)</t>
   </si>
   <si>
     <t>Model integrity checks</t>
@@ -795,8 +894,8 @@
     <numFmt numFmtId="166" formatCode="#,##0.0;\(#,##0.0\);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -860,13 +959,13 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF008000"/>
+      <color rgb="FF003255"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF003255"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -914,7 +1013,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -923,8 +1022,8 @@
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -942,21 +1041,21 @@
     <xf numFmtId="10" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -971,15 +1070,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1058,9 +1158,9 @@
           <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Football field'!$A$5:$A$9</c:f>
+              <c:f>'Football field'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>52-week range</c:v>
                 </c:pt>
@@ -1076,36 +1176,42 @@
                 <c:pt idx="4">
                   <c:v>P/E (peer 25th–75th pct)</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>EV/EBITDA regression (growth, margin ±1σ)</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Football field'!$B$5:$B$9</c:f>
+              <c:f>'Football field'!$B$5:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>42.15</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>68.860386900919735</c:v>
+                  <c:v>66.907100450329892</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45.228956776997194</c:v>
+                  <c:v>37.718789503680775</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>52.081035821902582</c:v>
+                  <c:v>42.572713780695963</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>41.415384305000003</c:v>
+                  <c:v>38.358736822499999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44.211384123598144</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2E4B-4AD3-83D3-983F6BAA19AF}"/>
+              <c16:uniqueId val="{00000000-8AB7-4A9D-9AB3-D4F94E76631B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1134,9 +1240,9 @@
           <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Football field'!$A$5:$A$9</c:f>
+              <c:f>'Football field'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>52-week range</c:v>
                 </c:pt>
@@ -1152,29 +1258,35 @@
                 <c:pt idx="4">
                   <c:v>P/E (peer 25th–75th pct)</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>EV/EBITDA regression (growth, margin ±1σ)</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Football field'!$D$5:$D$9</c:f>
+              <c:f>'Football field'!$D$5:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>25.65</c:v>
+                  <c:v>24.85</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.650990432865541</c:v>
+                  <c:v>16.075899171966682</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.253381745741983</c:v>
+                  <c:v>9.3865614985148085</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>72.599021276454948</c:v>
+                  <c:v>10.48547481531353</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.449720884999991</c:v>
+                  <c:v>15.69586718250001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35.416966182909626</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1193,7 +1305,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-2E4B-4AD3-83D3-983F6BAA19AF}"/>
+              <c16:uniqueId val="{00000001-8AB7-4A9D-9AB3-D4F94E76631B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1602,7 +1714,7 @@
       </c>
       <c r="B4" s="4">
         <f>Inputs!$B$5</f>
-        <v>47.35</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1611,7 +1723,7 @@
       </c>
       <c r="B5" s="4">
         <f>DCF!B21</f>
-        <v>75.763345013999682</v>
+        <v>73.995406865946137</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1620,7 +1732,7 @@
       </c>
       <c r="B6" s="4">
         <f>Scenarios!$I$8</f>
-        <v>77.794959855457378</v>
+        <v>76.102639409219051</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1629,7 +1741,7 @@
       </c>
       <c r="B7" s="4">
         <f>DCF!B30</f>
-        <v>78.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1638,7 +1750,7 @@
       </c>
       <c r="B8" s="5">
         <f>DCF!B31</f>
-        <v>0.65786694825765579</v>
+        <v>0.62447257383966259</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1647,7 +1759,7 @@
       </c>
       <c r="B9" s="5">
         <f>DCF!B32</f>
-        <v>0.73624276447298298</v>
+        <v>0.68776371308016881</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1692,7 +1804,7 @@
       </c>
       <c r="B14" s="8">
         <f>Peers!E22</f>
-        <v>8.1275372110804316</v>
+        <v>9.5143159715003502</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1701,7 +1813,7 @@
       </c>
       <c r="B15" s="8">
         <f>Peers!F22</f>
-        <v>8.4924439717599984</v>
+        <v>8.9872662844646616</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
@@ -1756,162 +1868,162 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="B5" s="53" t="b">
+        <v>257</v>
+      </c>
+      <c r="B5" s="54" t="b">
         <f>WACC!$B$17&gt;Inputs!$B$11</f>
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="53" t="b">
+        <v>259</v>
+      </c>
+      <c r="B6" s="54" t="b">
         <f>ABS(DCF!B16-(DCF!B10+DCF!B15))&lt;0.01</f>
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B7" s="53" t="b">
+        <v>261</v>
+      </c>
+      <c r="B7" s="54" t="b">
         <f>ABS(DCF!B19-(DCF!B16-Inputs!$B$8-Inputs!$B$9))&lt;0.01</f>
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="B8" s="53" t="b">
+        <v>263</v>
+      </c>
+      <c r="B8" s="54" t="b">
         <f>ABS(DCF!E41-DCF!B21)&lt;0.01</f>
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>231</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="B9" s="53" t="b">
+        <v>265</v>
+      </c>
+      <c r="B9" s="54" t="b">
         <f>ABS(Scenarios!I6-DCF!B21)&lt;0.01</f>
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="53" t="b">
+        <v>267</v>
+      </c>
+      <c r="B10" s="54" t="b">
         <f>Forecast!B6=Historicals!E5</f>
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="B11" s="53" t="b">
+        <v>269</v>
+      </c>
+      <c r="B11" s="54" t="b">
         <f>ABS(WACC!B15+WACC!B16-1)&lt;0.000001</f>
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="B12" s="53" t="b">
+        <v>271</v>
+      </c>
+      <c r="B12" s="54" t="b">
         <f>ABS(Scenarios!B8-1)&lt;0.000001</f>
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>239</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B13" s="53" t="b">
+        <v>273</v>
+      </c>
+      <c r="B13" s="54" t="b">
         <f>AND(Inputs!$B$5&gt;0,Inputs!$B$7&gt;0,Inputs!$B$6&gt;0)</f>
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>241</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B14" s="53" t="b">
+        <v>275</v>
+      </c>
+      <c r="B14" s="54" t="b">
         <f>DCF!B24&lt;0.85</f>
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>243</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="B15" s="53" t="b">
+        <v>277</v>
+      </c>
+      <c r="B15" s="54" t="b">
         <f>SUMPRODUCT(--ISERROR(Forecast!B5:I20))+SUMPRODUCT(--ISERROR(DCF!B5:G33))+SUMPRODUCT(--ISERROR(Scenarios!B5:J8))=0</f>
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B17" s="54" t="str">
+        <v>279</v>
+      </c>
+      <c r="B17" s="55" t="str">
         <f>IF(AND(B5:B15),"ALL OK","CHECK")</f>
         <v>ALL OK</v>
       </c>
@@ -1923,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1956,7 +2068,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="15">
-        <v>47.35</v>
+        <v>47.4</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>26</v>
@@ -1989,7 +2101,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="18">
-        <v>-579.88400000000001</v>
+        <v>-159.733</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
@@ -2091,12 +2203,12 @@
         <v>0</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="22">
         <v>0</v>
@@ -2107,249 +2219,271 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="22">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="B19" s="23">
+        <v>0.72826830937713893</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="21">
-        <v>0.10299999999999999</v>
+        <v>51</v>
+      </c>
+      <c r="B20" s="23">
+        <v>0.49555099247091028</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="23">
-        <v>3.7110948977957401</v>
+        <v>53</v>
+      </c>
+      <c r="B21" s="22">
+        <v>0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="22">
-        <v>12</v>
+        <v>55</v>
+      </c>
+      <c r="B22" s="21">
+        <v>0.10299999999999999</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="23">
-        <v>0.5</v>
+        <v>57</v>
+      </c>
+      <c r="B23" s="24">
+        <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="19">
-        <v>1</v>
+        <v>59</v>
+      </c>
+      <c r="B24" s="22">
+        <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="23">
-        <v>52.131006107002342</v>
+        <v>61</v>
+      </c>
+      <c r="B25" s="24">
+        <v>0.5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="19">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="19">
+        <v>64</v>
+      </c>
+      <c r="B27" s="24">
+        <v>46.766561751319131</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="19">
         <v>-0.1</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" s="14" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="B32" s="14" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
+      <c r="C32" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="24">
-        <v>1.47E-2</v>
-      </c>
-      <c r="C31" s="24">
-        <v>7.7600000000000002E-2</v>
-      </c>
-      <c r="D31" s="24">
-        <v>6.3200000000000006E-2</v>
-      </c>
-      <c r="E31" s="24">
-        <v>4.8800000000000003E-2</v>
-      </c>
-      <c r="F31" s="24">
-        <v>3.44E-2</v>
-      </c>
-      <c r="G31" s="24">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
+      <c r="D32" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="24">
-        <v>0.13456663034551269</v>
-      </c>
-      <c r="C32" s="24">
-        <v>0.13494101642716619</v>
-      </c>
-      <c r="D32" s="24">
-        <v>0.13531540250881971</v>
-      </c>
-      <c r="E32" s="24">
-        <v>0.1356897885904732</v>
-      </c>
-      <c r="F32" s="24">
-        <v>0.13606417467212659</v>
-      </c>
-      <c r="G32" s="24">
-        <v>0.13643856075378011</v>
+      <c r="E32" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="24">
-        <v>1.298214527978637E-2</v>
-      </c>
-      <c r="C33" s="24">
-        <v>1.298214527978637E-2</v>
-      </c>
-      <c r="D33" s="24">
-        <v>1.298214527978637E-2</v>
-      </c>
-      <c r="E33" s="24">
-        <v>1.298214527978637E-2</v>
-      </c>
-      <c r="F33" s="24">
-        <v>1.298214527978637E-2</v>
-      </c>
-      <c r="G33" s="24">
-        <v>1.298214527978637E-2</v>
+        <v>75</v>
+      </c>
+      <c r="B33" s="25">
+        <v>1.47E-2</v>
+      </c>
+      <c r="C33" s="25">
+        <v>7.7600000000000002E-2</v>
+      </c>
+      <c r="D33" s="25">
+        <v>6.3200000000000006E-2</v>
+      </c>
+      <c r="E33" s="25">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="F33" s="25">
+        <v>3.44E-2</v>
+      </c>
+      <c r="G33" s="25">
+        <v>0.02</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="24">
-        <v>1.022177785544261E-2</v>
-      </c>
-      <c r="C34" s="24">
-        <v>1.022177785544261E-2</v>
-      </c>
-      <c r="D34" s="24">
-        <v>1.022177785544261E-2</v>
-      </c>
-      <c r="E34" s="24">
-        <v>1.022177785544261E-2</v>
-      </c>
-      <c r="F34" s="24">
-        <v>1.022177785544261E-2</v>
-      </c>
-      <c r="G34" s="24">
-        <v>1.022177785544261E-2</v>
+        <v>76</v>
+      </c>
+      <c r="B34" s="25">
+        <v>0.13456663034551269</v>
+      </c>
+      <c r="C34" s="25">
+        <v>0.13494101642716619</v>
+      </c>
+      <c r="D34" s="25">
+        <v>0.13531540250881971</v>
+      </c>
+      <c r="E34" s="25">
+        <v>0.1356897885904732</v>
+      </c>
+      <c r="F34" s="25">
+        <v>0.13606417467212659</v>
+      </c>
+      <c r="G34" s="25">
+        <v>0.13643856075378011</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="24">
+        <v>77</v>
+      </c>
+      <c r="B35" s="25">
+        <v>1.298214527978637E-2</v>
+      </c>
+      <c r="C35" s="25">
+        <v>1.298214527978637E-2</v>
+      </c>
+      <c r="D35" s="25">
+        <v>1.298214527978637E-2</v>
+      </c>
+      <c r="E35" s="25">
+        <v>1.298214527978637E-2</v>
+      </c>
+      <c r="F35" s="25">
+        <v>1.298214527978637E-2</v>
+      </c>
+      <c r="G35" s="25">
+        <v>1.298214527978637E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="25">
+        <v>1.022177785544261E-2</v>
+      </c>
+      <c r="C36" s="25">
+        <v>1.022177785544261E-2</v>
+      </c>
+      <c r="D36" s="25">
+        <v>1.022177785544261E-2</v>
+      </c>
+      <c r="E36" s="25">
+        <v>1.022177785544261E-2</v>
+      </c>
+      <c r="F36" s="25">
+        <v>1.022177785544261E-2</v>
+      </c>
+      <c r="G36" s="25">
+        <v>1.022177785544261E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" s="25">
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C37" s="25">
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D37" s="25">
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E37" s="25">
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F37" s="25">
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G37" s="25">
         <v>-6.9648947052931273E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>76</v>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2368,34 +2502,34 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B5" s="18">
         <v>3085.47</v>
@@ -2411,26 +2545,26 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26">
+      <c r="A6" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27">
         <f>IF(B5=0,"",C5/B5-1)</f>
         <v>0.14269819508859283</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>IF(C5=0,"",D5/C5-1)</f>
         <v>0.11221350511279682</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>IF(D5=0,"",E5/D5-1)</f>
         <v>-2.3093798922272368E-3</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B7" s="18">
         <v>486.74299999999999</v>
@@ -2447,7 +2581,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B8" s="18">
         <v>51.39560000000003</v>
@@ -2464,49 +2598,49 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="27">
+        <v>93</v>
+      </c>
+      <c r="B9" s="28">
         <f>B7-B8</f>
         <v>435.34739999999999</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <f>C7-C8</f>
         <v>462.5225999999999</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>D7-D8</f>
         <v>564.44489250000004</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <f>E7-E8</f>
         <v>525.00608750000004</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="A10" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="27">
         <f>IF(B5=0,"",B9/B5)</f>
         <v>0.14109597565362814</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>IF(C5=0,"",C9/C5)</f>
         <v>0.13118376429939518</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>IF(D5=0,"",D9/D5)</f>
         <v>0.14393967369808583</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>IF(E5=0,"",E9/E5)</f>
         <v>0.13419224426385928</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B11" s="18">
         <v>79.046000000000006</v>
@@ -2523,7 +2657,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B12" s="18">
         <v>46.026000000000032</v>
@@ -2540,70 +2674,70 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="28">
+        <v>96</v>
+      </c>
+      <c r="B13" s="29">
         <f>MAX(B11-B12,0)</f>
         <v>33.019999999999975</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>MAX(C11-C12,0)</f>
         <v>42.354999999999968</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>MAX(D11-D12,0)</f>
         <v>63.739000000000004</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>MAX(E11-E12,0)</f>
         <v>41.781000000000056</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="27">
+        <v>97</v>
+      </c>
+      <c r="B14" s="28">
         <f>B9-B13</f>
         <v>402.32740000000001</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>C9-C13</f>
         <v>420.16759999999994</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>D9-D13</f>
         <v>500.7058925</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>E9-E13</f>
         <v>483.22508749999997</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="26">
+      <c r="A15" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="27">
         <f>IF(B5=0,"",B14/B5)</f>
         <v>0.13039420250399456</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <f>IF(C5=0,"",C14/C5)</f>
         <v>0.11917075490936566</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <f>IF(D5=0,"",D14/D5)</f>
         <v>0.12768552562491092</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>IF(E5=0,"",E14/E5)</f>
         <v>0.12351296588770463</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
-        <v>94</v>
+      <c r="A16" s="26" t="s">
+        <v>99</v>
       </c>
       <c r="B16" s="19">
         <v>0.21115253687793811</v>
@@ -2620,28 +2754,28 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" s="27">
+        <v>100</v>
+      </c>
+      <c r="B17" s="28">
         <f>B14*(1-B16)</f>
         <v>317.37494883449506</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>C14*(1-C16)</f>
         <v>326.65219693990218</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>D14*(1-D16)</f>
         <v>390.87286274267234</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>E14*(1-E16)</f>
         <v>366.78021900370652</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B18" s="18">
         <v>-41.018000000000001</v>
@@ -2658,7 +2792,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B19" s="18">
         <v>-106.325</v>
@@ -2675,49 +2809,49 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="27">
+        <v>103</v>
+      </c>
+      <c r="B20" s="28">
         <f>B17+B13+B18+B19</f>
         <v>203.05194883449502</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="28">
         <f>C17+C13+C18+C19</f>
         <v>386.60619693990213</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>D17+D13+D18+D19</f>
         <v>744.72986274267237</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>E17+E13+E18+E19</f>
         <v>275.94221900370655</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="B21" s="26">
+      <c r="A21" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="27">
         <f>IF(B5=0,"",B20/B5)</f>
         <v>6.5809082193148863E-2</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>IF(C5=0,"",C20/C5)</f>
         <v>0.10965184450673263</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>IF(D5=0,"",D20/D5)</f>
         <v>0.18991432974371453</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>IF(E5=0,"",E20/E5)</f>
         <v>7.0531192945942262E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B22" s="18">
         <v>315.70800000000003</v>
@@ -2734,24 +2868,24 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="23">
+        <v>106</v>
+      </c>
+      <c r="B23" s="24">
         <v>3.03</v>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="24">
         <v>3.13</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="24">
         <v>3.69</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>3.46</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B24" s="18">
         <v>367.09300000000002</v>
@@ -2768,7 +2902,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B25" s="18">
         <v>228.96299999999999</v>
@@ -2785,7 +2919,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B26" s="18">
         <v>228.96299999999999</v>
@@ -2802,7 +2936,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B27" s="18">
         <v>-367.09300000000002</v>
@@ -2819,28 +2953,28 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="29">
+        <v>111</v>
+      </c>
+      <c r="B28" s="30">
         <f>IF(B9&lt;=0,"n.m.",B27/B9)</f>
         <v>-0.84321854224924742</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="30">
         <f>IF(C9&lt;=0,"n.m.",C27/C9)</f>
         <v>-0.86065848457999694</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="30">
         <f>IF(D9&lt;=0,"n.m.",D27/D9)</f>
         <v>-1.3177442295662192</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="30">
         <f>IF(E9&lt;=0,"n.m.",E27/E9)</f>
         <v>-1.1045281451141269</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B29" s="18">
         <v>1.3424</v>
@@ -2871,603 +3005,603 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="30">
-        <f>Inputs!B31</f>
+        <v>75</v>
+      </c>
+      <c r="C5" s="31">
+        <f>Inputs!B33</f>
         <v>1.47E-2</v>
       </c>
-      <c r="D5" s="30">
-        <f>Inputs!C31</f>
+      <c r="D5" s="31">
+        <f>Inputs!C33</f>
         <v>7.7600000000000002E-2</v>
       </c>
-      <c r="E5" s="30">
-        <f>Inputs!D31</f>
+      <c r="E5" s="31">
+        <f>Inputs!D33</f>
         <v>6.3200000000000006E-2</v>
       </c>
-      <c r="F5" s="30">
-        <f>Inputs!E31</f>
+      <c r="F5" s="31">
+        <f>Inputs!E33</f>
         <v>4.8800000000000003E-2</v>
       </c>
-      <c r="G5" s="30">
-        <f>Inputs!F31</f>
+      <c r="G5" s="31">
+        <f>Inputs!F33</f>
         <v>3.44E-2</v>
       </c>
-      <c r="H5" s="30">
-        <f>Inputs!G31</f>
+      <c r="H5" s="31">
+        <f>Inputs!G33</f>
         <v>0.02</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <f>Inputs!$B$11</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="31">
+        <v>89</v>
+      </c>
+      <c r="B6" s="32">
         <f>Historicals!E5</f>
         <v>3912.3429999999998</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f t="shared" ref="C6:I6" si="0">B6*(1+C5)</f>
         <v>3969.8544420999997</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f t="shared" si="0"/>
         <v>4277.9151468069595</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <f t="shared" si="0"/>
         <v>4548.2793840851591</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <f t="shared" si="0"/>
         <v>4770.2354180285147</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="28">
         <f t="shared" si="0"/>
         <v>4934.3315164086953</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="28">
         <f t="shared" si="0"/>
         <v>5033.0181467368693</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="28">
         <f t="shared" si="0"/>
         <v>5133.6785096716067</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="26">
+      <c r="A7" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="27">
         <f>B8/B6</f>
         <v>0.13419224426385928</v>
       </c>
-      <c r="C7" s="30">
-        <f>Inputs!B32</f>
+      <c r="C7" s="31">
+        <f>Inputs!B34</f>
         <v>0.13456663034551269</v>
       </c>
-      <c r="D7" s="30">
-        <f>Inputs!C32</f>
+      <c r="D7" s="31">
+        <f>Inputs!C34</f>
         <v>0.13494101642716619</v>
       </c>
-      <c r="E7" s="30">
-        <f>Inputs!D32</f>
+      <c r="E7" s="31">
+        <f>Inputs!D34</f>
         <v>0.13531540250881971</v>
       </c>
-      <c r="F7" s="30">
-        <f>Inputs!E32</f>
+      <c r="F7" s="31">
+        <f>Inputs!E34</f>
         <v>0.1356897885904732</v>
       </c>
-      <c r="G7" s="30">
-        <f>Inputs!F32</f>
+      <c r="G7" s="31">
+        <f>Inputs!F34</f>
         <v>0.13606417467212659</v>
       </c>
-      <c r="H7" s="30">
-        <f>Inputs!G32</f>
+      <c r="H7" s="31">
+        <f>Inputs!G34</f>
         <v>0.13643856075378011</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <f>H7</f>
         <v>0.13643856075378011</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="31">
+        <v>93</v>
+      </c>
+      <c r="B8" s="32">
         <f>Historicals!E9</f>
         <v>525.00608750000004</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f t="shared" ref="C8:I8" si="1">C6*C7</f>
         <v>534.20993523556217</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f t="shared" si="1"/>
         <v>577.266218099301</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f t="shared" si="1"/>
         <v>615.45225558004995</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <f t="shared" si="1"/>
         <v>647.27223539907675</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="28">
         <f t="shared" si="1"/>
         <v>671.38574533881194</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="28">
         <f t="shared" si="1"/>
         <v>686.69775218843608</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="28">
         <f t="shared" si="1"/>
         <v>700.43170723220487</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="30">
-        <f>Inputs!B33</f>
+      <c r="A9" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="31">
+        <f>Inputs!B35</f>
         <v>1.298214527978637E-2</v>
       </c>
-      <c r="D9" s="30">
-        <f>Inputs!C33</f>
+      <c r="D9" s="31">
+        <f>Inputs!C35</f>
         <v>1.298214527978637E-2</v>
       </c>
-      <c r="E9" s="30">
-        <f>Inputs!D33</f>
+      <c r="E9" s="31">
+        <f>Inputs!D35</f>
         <v>1.298214527978637E-2</v>
       </c>
-      <c r="F9" s="30">
-        <f>Inputs!E33</f>
+      <c r="F9" s="31">
+        <f>Inputs!E35</f>
         <v>1.298214527978637E-2</v>
       </c>
-      <c r="G9" s="30">
-        <f>Inputs!F33</f>
+      <c r="G9" s="31">
+        <f>Inputs!F35</f>
         <v>1.298214527978637E-2</v>
       </c>
-      <c r="H9" s="30">
-        <f>Inputs!G33</f>
+      <c r="H9" s="31">
+        <f>Inputs!G35</f>
         <v>1.298214527978637E-2</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="27">
         <f>H9</f>
         <v>1.298214527978637E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="31">
+        <v>96</v>
+      </c>
+      <c r="B10" s="32">
         <f>Historicals!E13</f>
         <v>41.781000000000056</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f t="shared" ref="C10:I10" si="2">C6*C9</f>
         <v>51.537227106947462</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f t="shared" si="2"/>
         <v>55.536515930446583</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f t="shared" si="2"/>
         <v>59.046423737250805</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f t="shared" si="2"/>
         <v>61.927889215628646</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f t="shared" si="2"/>
         <v>64.058208604646268</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f t="shared" si="2"/>
         <v>65.339372776739197</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f t="shared" si="2"/>
         <v>66.646160232273971</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="31">
+        <v>97</v>
+      </c>
+      <c r="B11" s="32">
         <f>Historicals!E14</f>
         <v>483.22508749999997</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="28">
         <f t="shared" ref="C11:I11" si="3">C8-C10</f>
         <v>482.67270812861472</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="28">
         <f t="shared" si="3"/>
         <v>521.72970216885437</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="28">
         <f t="shared" si="3"/>
         <v>556.4058318427991</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="28">
         <f t="shared" si="3"/>
         <v>585.34434618344812</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="28">
         <f t="shared" si="3"/>
         <v>607.32753673416573</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="28">
         <f t="shared" si="3"/>
         <v>621.35837941169689</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="28">
         <f t="shared" si="3"/>
         <v>633.78554699993094</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="26">
+      <c r="A12" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="27">
         <f t="shared" ref="C12:I12" si="4">C11/C6</f>
         <v>0.12158448506572632</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f t="shared" si="4"/>
         <v>0.12195887114737981</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f t="shared" si="4"/>
         <v>0.12233325722903333</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f t="shared" si="4"/>
         <v>0.12270764331068684</v>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f t="shared" si="4"/>
         <v>0.12308202939234023</v>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="27">
         <f t="shared" si="4"/>
         <v>0.12345641547399373</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="27">
         <f t="shared" si="4"/>
         <v>0.12345641547399376</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="28">
+        <v>116</v>
+      </c>
+      <c r="C13" s="29">
         <f>-MAX(C11,0)*Inputs!$B$10</f>
         <v>-106.18799578829524</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>-MAX(D11,0)*Inputs!$B$10</f>
         <v>-114.78053447714797</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>-MAX(E11,0)*Inputs!$B$10</f>
         <v>-122.4092830054158</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <f>-MAX(F11,0)*Inputs!$B$10</f>
         <v>-128.77575616035858</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <f>-MAX(G11,0)*Inputs!$B$10</f>
         <v>-133.61205808151647</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="29">
         <f>-MAX(H11,0)*Inputs!$B$10</f>
         <v>-136.69884347057331</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="29">
         <f>-MAX(I11,0)*Inputs!$B$10</f>
         <v>-139.4328203399848</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="31">
+        <v>100</v>
+      </c>
+      <c r="B14" s="32">
         <f>Historicals!E17</f>
         <v>366.78021900370652</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f t="shared" ref="C14:I14" si="5">C11+C13</f>
         <v>376.48471234031945</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f t="shared" si="5"/>
         <v>406.94916769170641</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f t="shared" si="5"/>
         <v>433.99654883738333</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f t="shared" si="5"/>
         <v>456.56859002308954</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="28">
         <f t="shared" si="5"/>
         <v>473.71547865264927</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="28">
         <f t="shared" si="5"/>
         <v>484.65953594112358</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="28">
         <f t="shared" si="5"/>
         <v>494.35272665994614</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="30">
-        <f>Inputs!B34</f>
+      <c r="A15" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="31">
+        <f>Inputs!B36</f>
         <v>1.022177785544261E-2</v>
       </c>
-      <c r="D15" s="30">
-        <f>Inputs!C34</f>
+      <c r="D15" s="31">
+        <f>Inputs!C36</f>
         <v>1.022177785544261E-2</v>
       </c>
-      <c r="E15" s="30">
-        <f>Inputs!D34</f>
+      <c r="E15" s="31">
+        <f>Inputs!D36</f>
         <v>1.022177785544261E-2</v>
       </c>
-      <c r="F15" s="30">
-        <f>Inputs!E34</f>
+      <c r="F15" s="31">
+        <f>Inputs!E36</f>
         <v>1.022177785544261E-2</v>
       </c>
-      <c r="G15" s="30">
-        <f>Inputs!F34</f>
+      <c r="G15" s="31">
+        <f>Inputs!F36</f>
         <v>1.022177785544261E-2</v>
       </c>
-      <c r="H15" s="30">
-        <f>Inputs!G34</f>
+      <c r="H15" s="31">
+        <f>Inputs!G36</f>
         <v>1.022177785544261E-2</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="27">
         <f>H15</f>
         <v>1.022177785544261E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="31">
+        <v>101</v>
+      </c>
+      <c r="B16" s="32">
         <f>Historicals!E18</f>
         <v>-26.32</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f t="shared" ref="C16:I16" si="6">-C6*C15</f>
         <v>-40.578970225588257</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f t="shared" si="6"/>
         <v>-43.727898315093903</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f t="shared" si="6"/>
         <v>-46.491501488607838</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f t="shared" si="6"/>
         <v>-48.760286761251898</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f t="shared" si="6"/>
         <v>-50.437640625838959</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f t="shared" si="6"/>
         <v>-51.446393438355734</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f t="shared" si="6"/>
         <v>-52.475321307122854</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="30">
-        <f>Inputs!B35</f>
+      <c r="A17" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="31">
+        <f>Inputs!B37</f>
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="D17" s="30">
-        <f>Inputs!C35</f>
+      <c r="D17" s="31">
+        <f>Inputs!C37</f>
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="E17" s="30">
-        <f>Inputs!D35</f>
+      <c r="E17" s="31">
+        <f>Inputs!D37</f>
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="F17" s="30">
-        <f>Inputs!E35</f>
+      <c r="F17" s="31">
+        <f>Inputs!E37</f>
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="G17" s="30">
-        <f>Inputs!F35</f>
+      <c r="G17" s="31">
+        <f>Inputs!F37</f>
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="H17" s="30">
-        <f>Inputs!G35</f>
+      <c r="H17" s="31">
+        <f>Inputs!G37</f>
         <v>-6.9648947052931273E-2</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="27">
         <f>H17</f>
         <v>-6.9648947052931273E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="31">
+        <v>102</v>
+      </c>
+      <c r="B18" s="32">
         <f>Historicals!E19</f>
         <v>-106.29900000000001</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f t="shared" ref="C18:I18" si="7">-C17*(C6-B6)</f>
         <v>4.005611385760611</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f t="shared" si="7"/>
         <v>21.456103711223736</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f t="shared" si="7"/>
         <v>18.830584447195474</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f t="shared" si="7"/>
         <v>15.459004056199388</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <f t="shared" si="7"/>
         <v>11.429120467673799</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="29">
         <f t="shared" si="7"/>
         <v>6.8734198905591946</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="29">
         <f t="shared" si="7"/>
         <v>7.0108882883703671</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="31">
+        <v>103</v>
+      </c>
+      <c r="B19" s="32">
         <f>Historicals!E20</f>
         <v>275.94221900370655</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f t="shared" ref="C19:I19" si="8">C14+C10+C16+C18</f>
         <v>391.44858060743928</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f t="shared" si="8"/>
         <v>440.21388901828283</v>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f t="shared" si="8"/>
         <v>465.38205553322172</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="28">
         <f t="shared" si="8"/>
         <v>485.19519653366564</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="28">
         <f t="shared" si="8"/>
         <v>498.76516709913028</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="28">
         <f t="shared" si="8"/>
         <v>505.42593517006628</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="28">
         <f t="shared" si="8"/>
         <v>515.53445387346756</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="26">
+      <c r="A20" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="27">
         <f t="shared" ref="C20:I20" si="9">C19/C6</f>
         <v>9.8605272892667628E-2</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="27">
         <f t="shared" si="9"/>
         <v>0.10290383841457421</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f t="shared" si="9"/>
         <v>0.10232046368163654</v>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f t="shared" si="9"/>
         <v>0.10171305061799055</v>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="27">
         <f t="shared" si="9"/>
         <v>0.1010805953026321</v>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="27">
         <f t="shared" si="9"/>
         <v>0.10042203712254773</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="27">
         <f t="shared" si="9"/>
         <v>0.10042203712254773</v>
       </c>
@@ -3479,7 +3613,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3489,17 +3623,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>24</v>
@@ -3546,9 +3680,9 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="32">
+        <v>120</v>
+      </c>
+      <c r="B9" s="33">
         <f>B5+B6*B7+B8</f>
         <v>8.3000000000000004E-2</v>
       </c>
@@ -3573,45 +3707,45 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" s="33">
+        <v>121</v>
+      </c>
+      <c r="B12" s="34">
         <f>B10*(1-B11)</f>
         <v>4.5240000000000002E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="28">
+        <v>122</v>
+      </c>
+      <c r="B13" s="29">
         <f>(Inputs!$B$5*Inputs!$B$6)*Inputs!$B$7</f>
-        <v>4846.8905121999996</v>
+        <v>4852.0086647999997</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="31">
+        <v>123</v>
+      </c>
+      <c r="B14" s="32">
         <f>Inputs!$B$17</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="34">
+        <v>124</v>
+      </c>
+      <c r="B15" s="35">
         <f>B13/(B13+B14)</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="34">
+        <v>125</v>
+      </c>
+      <c r="B16" s="35">
         <f>B14/(B13+B14)</f>
         <v>0</v>
       </c>
@@ -3620,9 +3754,46 @@
       <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="33">
         <f>B15*B9+B16*B12</f>
         <v>8.3000000000000004E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="24">
+        <v>0.67472609130785877</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" s="24">
+        <v>0.67472609130785877</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="24">
+        <v>0.78206648117626543</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="22">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3641,160 +3812,160 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="35">
+        <v>103</v>
+      </c>
+      <c r="B5" s="36">
         <f>Forecast!C19</f>
         <v>391.44858060743928</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="36">
         <f>Forecast!D19</f>
         <v>440.21388901828283</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="36">
         <f>Forecast!E19</f>
         <v>465.38205553322172</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="36">
         <f>Forecast!F19</f>
         <v>485.19519653366564</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="36">
         <f>Forecast!G19</f>
         <v>498.76516709913028</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="36">
         <f>Forecast!H19</f>
         <v>505.42593517006628</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="36">
-        <f>1-0.5*Inputs!$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="36">
-        <f>2-0.5*Inputs!$B$18</f>
-        <v>2</v>
-      </c>
-      <c r="D6" s="36">
-        <f>3-0.5*Inputs!$B$18</f>
-        <v>3</v>
-      </c>
-      <c r="E6" s="36">
-        <f>4-0.5*Inputs!$B$18</f>
-        <v>4</v>
-      </c>
-      <c r="F6" s="36">
-        <f>5-0.5*Inputs!$B$18</f>
-        <v>5</v>
-      </c>
-      <c r="G6" s="36">
-        <f>6-0.5*Inputs!$B$18</f>
-        <v>6</v>
+        <v>134</v>
+      </c>
+      <c r="B6" s="37">
+        <f>IF(Inputs!$B$18=1,(1+Inputs!$B$20)/2,1)-Inputs!$B$19</f>
+        <v>0.27173169062286107</v>
+      </c>
+      <c r="C6" s="37">
+        <f>2-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>1.2717316906228611</v>
+      </c>
+      <c r="D6" s="37">
+        <f>3-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>2.2717316906228611</v>
+      </c>
+      <c r="E6" s="37">
+        <f>4-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>3.2717316906228611</v>
+      </c>
+      <c r="F6" s="37">
+        <f>5-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>4.2717316906228611</v>
+      </c>
+      <c r="G6" s="37">
+        <f>6-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>5.2717316906228611</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B7" s="37">
         <f>1/(1+WACC!$B$17)^B6</f>
-        <v>0.92336103416435833</v>
+        <v>0.97856651529371275</v>
       </c>
       <c r="C7" s="37">
         <f>1/(1+WACC!$B$17)^C6</f>
-        <v>0.85259559941307328</v>
+        <v>0.90357018956021495</v>
       </c>
       <c r="D7" s="37">
         <f>1/(1+WACC!$B$17)^D6</f>
-        <v>0.78725355439803635</v>
+        <v>0.83432150467240529</v>
       </c>
       <c r="E7" s="37">
         <f>1/(1+WACC!$B$17)^E6</f>
-        <v>0.72691925613853769</v>
+        <v>0.77037996737987569</v>
       </c>
       <c r="F7" s="37">
         <f>1/(1+WACC!$B$17)^F6</f>
-        <v>0.67120891610206623</v>
+        <v>0.71133884337938658</v>
       </c>
       <c r="G7" s="37">
         <f>1/(1+WACC!$B$17)^G6</f>
-        <v>0.61976815891234194</v>
+        <v>0.65682257006406897</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="27">
-        <f t="shared" ref="B8:G8" si="0">B5*B7</f>
-        <v>361.44836621185533</v>
-      </c>
-      <c r="C8" s="27">
-        <f t="shared" si="0"/>
-        <v>375.32442457750295</v>
-      </c>
-      <c r="D8" s="27">
-        <f t="shared" si="0"/>
-        <v>366.37367737159315</v>
-      </c>
-      <c r="E8" s="27">
-        <f t="shared" si="0"/>
-        <v>352.69773134624381</v>
-      </c>
-      <c r="F8" s="27">
-        <f t="shared" si="0"/>
-        <v>334.77562719807321</v>
-      </c>
-      <c r="G8" s="27">
-        <f t="shared" si="0"/>
-        <v>313.24690130690067</v>
+        <v>136</v>
+      </c>
+      <c r="B8" s="28">
+        <f>B5*(1-Inputs!$B$20)*B7</f>
+        <v>193.23346675326965</v>
+      </c>
+      <c r="C8" s="28">
+        <f>C5*C7</f>
+        <v>397.76414714728924</v>
+      </c>
+      <c r="D8" s="28">
+        <f>D5*D7</f>
+        <v>388.27825682001441</v>
+      </c>
+      <c r="E8" s="28">
+        <f>E5*E7</f>
+        <v>373.78465967847768</v>
+      </c>
+      <c r="F8" s="28">
+        <f>F5*F7</f>
+        <v>354.79103708222181</v>
+      </c>
+      <c r="G8" s="28">
+        <f>G5*G7</f>
+        <v>331.97516171543845</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="27">
+        <v>137</v>
+      </c>
+      <c r="B10" s="28">
         <f>SUM(B8:G8)</f>
-        <v>2103.866728012169</v>
+        <v>2039.8267291967113</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -3817,65 +3988,65 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="28">
-        <f>IF(Inputs!$B$19=1,Forecast!$H$14*(1+B11)*(1-B11/Inputs!$B$20),$G$5*(1+B11))</f>
+        <v>138</v>
+      </c>
+      <c r="B13" s="29">
+        <f>IF(Inputs!$B$21=1,Forecast!$H$14*(1+B11)*(1-B11/Inputs!$B$22),$G$5*(1+B11))</f>
         <v>515.53445387346767</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="27">
+        <v>139</v>
+      </c>
+      <c r="B14" s="28">
         <f>B13/(B12-B11)</f>
         <v>8183.086569420122</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="27">
-        <f>B14/(1+B12)^6</f>
-        <v>5071.6164973498207</v>
+        <v>140</v>
+      </c>
+      <c r="B15" s="28">
+        <f>B14/(1+B12)^(6-Inputs!$B$19)</f>
+        <v>5374.8359515832899</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="27">
+        <v>141</v>
+      </c>
+      <c r="B16" s="28">
         <f>B10+B15</f>
-        <v>7175.4832253619898</v>
+        <v>7414.6626807800012</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="31">
+        <v>142</v>
+      </c>
+      <c r="B17" s="32">
         <f>-Inputs!$B$8</f>
-        <v>579.88400000000001</v>
+        <v>159.733</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="31">
+        <v>143</v>
+      </c>
+      <c r="B18" s="32">
         <f>-Inputs!$B$9</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="27">
+        <v>144</v>
+      </c>
+      <c r="B19" s="28">
         <f>B16+B17+B18</f>
-        <v>7755.3672253619898</v>
+        <v>7574.3956807800014</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -3889,61 +4060,61 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B21" s="39">
         <f>B19/B20/Inputs!$B$6</f>
-        <v>75.763345013999682</v>
+        <v>73.995406865946137</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B22" s="4">
         <f>Inputs!$B$5</f>
-        <v>47.35</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B23" s="40">
         <f>B21/B22-1</f>
-        <v>0.60007064443505143</v>
+        <v>0.56108453303683836</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B24" s="34">
+        <v>148</v>
+      </c>
+      <c r="B24" s="35">
         <f>B15/B16</f>
-        <v>0.7067979030909054</v>
+        <v>0.72489284853318137</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="B25" s="29">
+        <v>149</v>
+      </c>
+      <c r="B25" s="30">
         <f>B14/Forecast!H8</f>
         <v>11.916576897683814</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B26" s="4">
-        <f>Inputs!$B$24*B21+(1-Inputs!$B$24)*Inputs!$B$25</f>
-        <v>75.763345013999682</v>
+        <f>Inputs!$B$26*B21+(1-Inputs!$B$26)*Inputs!$B$27</f>
+        <v>73.995406865946137</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B27" s="7">
         <f>WACC!$B$9</f>
@@ -3952,20 +4123,20 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B28" s="41">
-        <f>IF(Inputs!$B$22&gt;0,Inputs!$B$21,0)</f>
-        <v>3.7110948977957401</v>
+        <f>IF(Inputs!$B$24&gt;0,Inputs!$B$23,0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B29" s="41">
-        <f>IF(B26&lt;=0,0,B26*(1+B27)^(Inputs!$B$22/12)-B28)</f>
-        <v>78.340607752365912</v>
+        <f>IF(B26&lt;=0,0,B26*(1+B27)^(Inputs!$B$24/12)-B28)</f>
+        <v>77.137025635819668</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -3973,8 +4144,8 @@
         <v>5</v>
       </c>
       <c r="B30" s="39">
-        <f>IF(Inputs!$B$23&gt;0,MROUND(B29,Inputs!$B$23),B29)</f>
-        <v>78.5</v>
+        <f>IF(Inputs!$B$25&gt;0,MROUND(B29,Inputs!$B$25),B29)</f>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -3983,16 +4154,16 @@
       </c>
       <c r="B31" s="40">
         <f>B30/B22-1</f>
-        <v>0.65786694825765579</v>
+        <v>0.62447257383966259</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B32" s="40">
         <f>(B30+B28)/B22-1</f>
-        <v>0.73624276447298298</v>
+        <v>0.68776371308016881</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -4000,18 +4171,18 @@
         <v>8</v>
       </c>
       <c r="B33" s="3" t="str">
-        <f>IF(B26&lt;=0,"NOT RATED",IF(B32&gt;=Inputs!$B$26,"BUY",IF(B32&lt;=Inputs!$B$27,"SELL","HOLD")))</f>
+        <f>IF(B26&lt;=0,"NOT RATED",IF(B32&gt;=Inputs!$B$28,"BUY",IF(B32&lt;=Inputs!$B$29,"SELL","HOLD")))</f>
         <v>BUY</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B37" s="42">
         <f>WACC!$B$17+(-3)*0.005</f>
@@ -4048,32 +4219,32 @@
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="B38" s="43">
-        <f>IF(B$37&lt;=$A38,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(B$37-$A38)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>87.925230841746753</v>
+        <f>IF(B$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(B$37-$A38)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>85.99636321598912</v>
       </c>
       <c r="C38" s="43">
-        <f>IF(C$37&lt;=$A38,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(C$37-$A38)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>81.025869788231219</v>
+        <f>IF(C$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(C$37-$A38)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>79.030142024311644</v>
       </c>
       <c r="D38" s="43">
-        <f>IF(D$37&lt;=$A38,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(D$37-$A38)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>75.181279238851758</v>
+        <f>IF(D$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(D$37-$A38)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>73.12834473702047</v>
       </c>
       <c r="E38" s="43">
-        <f>IF(E$37&lt;=$A38,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(E$37-$A38)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>70.167011208245839</v>
+        <f>IF(E$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(E$37-$A38)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>68.064482050959697</v>
       </c>
       <c r="F38" s="43">
-        <f>IF(F$37&lt;=$A38,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(F$37-$A38)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>65.818074861139081</v>
+        <f>IF(F$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(F$37-$A38)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>63.67206220145642</v>
       </c>
       <c r="G38" s="43">
-        <f>IF(G$37&lt;=$A38,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(G$37-$A38)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>62.010471536662124</v>
+        <f>IF(G$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(G$37-$A38)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>59.825958175967102</v>
       </c>
       <c r="H38" s="43">
-        <f>IF(H$37&lt;=$A38,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(H$37-$A38)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>58.649208712287788</v>
+        <f>IF(H$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(H$37-$A38)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>56.43031274783889</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -4082,32 +4253,32 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="B39" s="43">
-        <f>IF(B$37&lt;=$A39,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(B$37-$A39)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>90.945385545380702</v>
+        <f>IF(B$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(B$37-$A39)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>89.164739308647725</v>
       </c>
       <c r="C39" s="43">
-        <f>IF(C$37&lt;=$A39,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(C$37-$A39)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>83.499144333852854</v>
+        <f>IF(C$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(C$37-$A39)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>81.633639348419933</v>
       </c>
       <c r="D39" s="43">
-        <f>IF(D$37&lt;=$A39,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(D$37-$A39)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>77.236122271664485</v>
+        <f>IF(D$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(D$37-$A39)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>75.298715158182475</v>
       </c>
       <c r="E39" s="43">
-        <f>IF(E$37&lt;=$A39,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(E$37-$A39)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>71.895290765905102</v>
+        <f>IF(E$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(E$37-$A39)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>69.896091184999619</v>
       </c>
       <c r="F39" s="43">
-        <f>IF(F$37&lt;=$A39,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(F$37-$A39)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>67.287136496786587</v>
+        <f>IF(F$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(F$37-$A39)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>65.234186835330235</v>
       </c>
       <c r="G39" s="43">
-        <f>IF(G$37&lt;=$A39,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(G$37-$A39)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>63.270739838613586</v>
+        <f>IF(G$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(G$37-$A39)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>61.170545006116356</v>
       </c>
       <c r="H39" s="43">
-        <f>IF(H$37&lt;=$A39,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(H$37-$A39)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>59.739138189412273</v>
+        <f>IF(H$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(H$37-$A39)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>57.597035845831499</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -4116,32 +4287,32 @@
         <v>1.7500000000000002E-2</v>
       </c>
       <c r="B40" s="43">
-        <f>IF(B$37&lt;=$A40,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(B$37-$A40)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>94.264565467196235</v>
+        <f>IF(B$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(B$37-$A40)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>92.646816004539872</v>
       </c>
       <c r="C40" s="43">
-        <f>IF(C$37&lt;=$A40,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(C$37-$A40)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>86.195236406107099</v>
+        <f>IF(C$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(C$37-$A40)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>84.471685981006502</v>
       </c>
       <c r="D40" s="43">
-        <f>IF(D$37&lt;=$A40,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(D$37-$A40)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>79.460787042726224</v>
+        <f>IF(D$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(D$37-$A40)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>77.648455035638861</v>
       </c>
       <c r="E40" s="43">
-        <f>IF(E$37&lt;=$A40,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(E$37-$A40)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>73.755500060790283</v>
+        <f>IF(E$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(E$37-$A40)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>71.867517810187636</v>
       </c>
       <c r="F40" s="43">
-        <f>IF(F$37&lt;=$A40,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(F$37-$A40)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>68.860386900919735</v>
+        <f>IF(F$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(F$37-$A40)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>66.907100450329892</v>
       </c>
       <c r="G40" s="43">
-        <f>IF(G$37&lt;=$A40,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(G$37-$A40)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>64.614469617515496</v>
+        <f>IF(G$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(G$37-$A40)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>62.604177321705968</v>
       </c>
       <c r="H40" s="43">
-        <f>IF(H$37&lt;=$A40,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(H$37-$A40)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>60.896765149587971</v>
+        <f>IF(H$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(H$37-$A40)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>58.836226216991356</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -4150,32 +4321,32 @@
         <v>0.02</v>
       </c>
       <c r="B41" s="43">
-        <f>IF(B$37&lt;=$A41,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(B$37-$A41)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>97.929493297534222</v>
+        <f>IF(B$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(B$37-$A41)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>96.491609022920755</v>
       </c>
       <c r="C41" s="43">
-        <f>IF(C$37&lt;=$A41,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(C$37-$A41)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>89.145676787064545</v>
+        <f>IF(C$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(C$37-$A41)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>87.577472861950284</v>
       </c>
       <c r="D41" s="43">
-        <f>IF(D$37&lt;=$A41,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(D$37-$A41)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>81.877233259569138</v>
+        <f>IF(D$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(D$37-$A41)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>80.20075869563459</v>
       </c>
       <c r="E41" s="44">
-        <f>IF(E$37&lt;=$A41,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(E$37-$A41)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>75.763345013999682</v>
+        <f>IF(E$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(E$37-$A41)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>73.995406865946137</v>
       </c>
       <c r="F41" s="43">
-        <f>IF(F$37&lt;=$A41,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(F$37-$A41)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>70.549317481827387</v>
+        <f>IF(F$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(F$37-$A41)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>68.703022419373625</v>
       </c>
       <c r="G41" s="43">
-        <f>IF(G$37&lt;=$A41,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(G$37-$A41)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>66.05023568264356</v>
+        <f>IF(G$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(G$37-$A41)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>64.136003631514043</v>
       </c>
       <c r="H41" s="43">
-        <f>IF(H$37&lt;=$A41,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(H$37-$A41)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>62.12859896618518</v>
+        <f>IF(H$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(H$37-$A41)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>60.154851868353767</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -4184,32 +4355,32 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="B42" s="43">
-        <f>IF(B$37&lt;=$A42,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(B$37-$A42)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>101.99716044988733</v>
+        <f>IF(B$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(B$37-$A42)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>100.75890676859622</v>
       </c>
       <c r="C42" s="43">
-        <f>IF(C$37&lt;=$A42,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(C$37-$A42)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>92.388239978017765</v>
+        <f>IF(C$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(C$37-$A42)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>90.990763394472594</v>
       </c>
       <c r="D42" s="43">
-        <f>IF(D$37&lt;=$A42,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(D$37-$A42)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>84.511377333785276</v>
+        <f>IF(D$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(D$37-$A42)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>82.982999622296575</v>
       </c>
       <c r="E42" s="43">
-        <f>IF(E$37&lt;=$A42,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(E$37-$A42)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>77.937127566647845</v>
+        <f>IF(E$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(E$37-$A42)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>76.299154521354069</v>
       </c>
       <c r="F42" s="43">
-        <f>IF(F$37&lt;=$A42,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(F$37-$A42)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>72.367174061277581</v>
+        <f>IF(F$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(F$37-$A42)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>70.636037668497011</v>
       </c>
       <c r="G42" s="43">
-        <f>IF(G$37&lt;=$A42,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(G$37-$A42)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>67.587829128277136</v>
+        <f>IF(G$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(G$37-$A42)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>65.776470105138273</v>
       </c>
       <c r="H42" s="43">
-        <f>IF(H$37&lt;=$A42,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(H$37-$A42)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>63.44201118123253</v>
+        <f>IF(H$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(H$37-$A42)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>61.560803721793143</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -4218,32 +4389,32 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="B43" s="43">
-        <f>IF(B$37&lt;=$A43,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(B$37-$A43)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>106.53781215483966</v>
+        <f>IF(B$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(B$37-$A43)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>105.52240192655957</v>
       </c>
       <c r="C43" s="43">
-        <f>IF(C$37&lt;=$A43,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(C$37-$A43)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>95.968570168028634</v>
+        <f>IF(C$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(C$37-$A43)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>94.759605024132696</v>
       </c>
       <c r="D43" s="43">
-        <f>IF(D$37&lt;=$A43,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(D$37-$A43)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>87.39402556594635</v>
+        <f>IF(D$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(D$37-$A43)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>86.027716108077655</v>
       </c>
       <c r="E43" s="43">
-        <f>IF(E$37&lt;=$A43,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(E$37-$A43)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>80.298305166938093</v>
+        <f>IF(E$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(E$37-$A43)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>78.80150111257305</v>
       </c>
       <c r="F43" s="43">
-        <f>IF(F$37&lt;=$A43,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(F$37-$A43)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>74.329304972430194</v>
+        <f>IF(F$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(F$37-$A43)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>72.722466826280993</v>
       </c>
       <c r="G43" s="43">
-        <f>IF(G$37&lt;=$A43,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(G$37-$A43)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>69.238480915501427</v>
+        <f>IF(G$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(G$37-$A43)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>67.537559113587832</v>
       </c>
       <c r="H43" s="43">
-        <f>IF(H$37&lt;=$A43,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(H$37-$A43)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>64.845383137036549</v>
+        <f>IF(H$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(H$37-$A43)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>63.063053647385914</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -4252,32 +4423,32 @@
         <v>2.75E-2</v>
       </c>
       <c r="B44" s="43">
-        <f>IF(B$37&lt;=$A44,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(B$37-$A44)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>111.63903814435403</v>
+        <f>IF(B$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(B$37-$A44)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>110.87398290649371</v>
       </c>
       <c r="C44" s="43">
-        <f>IF(C$37&lt;=$A44,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(C$37-$A44)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>99.942343236062655</v>
+        <f>IF(C$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(C$37-$A44)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>98.942605074634557</v>
       </c>
       <c r="D44" s="43">
-        <f>IF(D$37&lt;=$A44,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(D$37-$A44)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>90.562084514162962</v>
+        <f>IF(D$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(D$37-$A44)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>89.37388967165883</v>
       </c>
       <c r="E44" s="43">
-        <f>IF(E$37&lt;=$A44,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(E$37-$A44)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>82.872201469957233</v>
+        <f>IF(E$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(E$37-$A44)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>81.52928433363158</v>
       </c>
       <c r="F44" s="43">
-        <f>IF(F$37&lt;=$A44,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(F$37-$A44)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>76.45359546301691</v>
+        <f>IF(F$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(F$37-$A44)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>74.981328145865319</v>
       </c>
       <c r="G44" s="43">
-        <f>IF(G$37&lt;=$A44,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(G$37-$A44)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>71.015136655948965</v>
+        <f>IF(G$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(G$37-$A44)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>69.433082397491575</v>
       </c>
       <c r="H44" s="43">
-        <f>IF(H$37&lt;=$A44,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(H$37-$A44)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>66.348285018784139</v>
+        <f>IF(H$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(H$37-$A44)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>64.671846120893065</v>
       </c>
     </row>
   </sheetData>
@@ -4296,32 +4467,32 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>10</v>
@@ -4330,15 +4501,15 @@
         <v>11</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B5" s="19">
         <v>0.25</v>
@@ -4355,26 +4526,26 @@
       <c r="F5" s="21">
         <v>-2.5000000000000001E-3</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="34">
         <f>WACC!$B$17+E5</f>
         <v>8.8000000000000009E-2</v>
       </c>
-      <c r="H5" s="33">
+      <c r="H5" s="34">
         <f>Inputs!$B$11+F5</f>
         <v>1.7500000000000002E-2</v>
       </c>
       <c r="I5" s="45">
         <f>B25</f>
-        <v>55.458239984310303</v>
-      </c>
-      <c r="J5" s="34">
+        <v>52.933293962086459</v>
+      </c>
+      <c r="J5" s="35">
         <f>I5/Inputs!$B$5-1</f>
-        <v>0.17124054877107286</v>
+        <v>0.11673615953768901</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B6" s="19">
         <v>0.5</v>
@@ -4391,26 +4562,26 @@
       <c r="F6" s="21">
         <v>0</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="34">
         <f>WACC!$B$17+E6</f>
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="H6" s="33">
+      <c r="H6" s="34">
         <f>Inputs!$B$11+F6</f>
         <v>0.02</v>
       </c>
       <c r="I6" s="45">
         <f>B40</f>
-        <v>75.763345013999682</v>
-      </c>
-      <c r="J6" s="34">
+        <v>73.995406865946137</v>
+      </c>
+      <c r="J6" s="35">
         <f>I6/Inputs!$B$5-1</f>
-        <v>0.60007064443505143</v>
+        <v>0.56108453303683836</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B7" s="19">
         <v>0.25</v>
@@ -4427,26 +4598,26 @@
       <c r="F7" s="21">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="34">
         <f>WACC!$B$17+E7</f>
         <v>7.8E-2</v>
       </c>
-      <c r="H7" s="33">
+      <c r="H7" s="34">
         <f>Inputs!$B$11+F7</f>
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="I7" s="45">
         <f>B55</f>
-        <v>104.19490940951984</v>
-      </c>
-      <c r="J7" s="34">
+        <v>103.48644994289751</v>
+      </c>
+      <c r="J7" s="35">
         <f>I7/Inputs!$B$5-1</f>
-        <v>1.2005260698948224</v>
+        <v>1.1832584376138717</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B8" s="40">
         <f>SUM(B5:B7)</f>
@@ -4454,1115 +4625,1115 @@
       </c>
       <c r="I8" s="39">
         <f>IFERROR(SUMPRODUCT(B5:B7,I5:I7)/B8,"")</f>
-        <v>77.794959855457378</v>
+        <v>76.102639409219051</v>
       </c>
       <c r="J8" s="40">
         <f>IFERROR(I8/Inputs!$B$5-1,"")</f>
-        <v>0.64297697688399946</v>
+        <v>0.6055409158063092</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B12" s="46" t="str">
         <f>Forecast!B4</f>
         <v>2025A</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="26">
-        <f>Inputs!B31+$C$5</f>
+      <c r="A13" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="27">
+        <f>Inputs!B33+$C$5</f>
         <v>-5.3000000000000009E-3</v>
       </c>
-      <c r="D13" s="26">
-        <f>Inputs!C31+$C$5</f>
+      <c r="D13" s="27">
+        <f>Inputs!C33+$C$5</f>
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="E13" s="26">
-        <f>Inputs!D31+$C$5</f>
+      <c r="E13" s="27">
+        <f>Inputs!D33+$C$5</f>
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="F13" s="26">
-        <f>Inputs!E31+$C$5</f>
+      <c r="F13" s="27">
+        <f>Inputs!E33+$C$5</f>
         <v>2.8800000000000003E-2</v>
       </c>
-      <c r="G13" s="26">
-        <f>Inputs!F31+$C$5</f>
+      <c r="G13" s="27">
+        <f>Inputs!F33+$C$5</f>
         <v>1.44E-2</v>
       </c>
-      <c r="H13" s="26">
-        <f>Inputs!G31+$C$5</f>
+      <c r="H13" s="27">
+        <f>Inputs!G33+$C$5</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="31">
+        <v>89</v>
+      </c>
+      <c r="B14" s="32">
         <f>Forecast!B6</f>
         <v>3912.3429999999998</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f t="shared" ref="C14:H14" si="0">B14*(1+C13)</f>
         <v>3891.6075820999999</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f t="shared" si="0"/>
         <v>4115.7641788289602</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f t="shared" si="0"/>
         <v>4293.5651913543707</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f t="shared" si="0"/>
         <v>4417.2198688653762</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="28">
         <f t="shared" si="0"/>
         <v>4480.8278349770371</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="28">
         <f t="shared" si="0"/>
         <v>4480.8278349770371</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="26">
-        <f>Inputs!B32+$D$5</f>
+      <c r="A15" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="27">
+        <f>Inputs!B34+$D$5</f>
         <v>0.11956663034551269</v>
       </c>
-      <c r="D15" s="26">
-        <f>Inputs!C32+$D$5</f>
+      <c r="D15" s="27">
+        <f>Inputs!C34+$D$5</f>
         <v>0.11994101642716619</v>
       </c>
-      <c r="E15" s="26">
-        <f>Inputs!D32+$D$5</f>
+      <c r="E15" s="27">
+        <f>Inputs!D34+$D$5</f>
         <v>0.12031540250881971</v>
       </c>
-      <c r="F15" s="26">
-        <f>Inputs!E32+$D$5</f>
+      <c r="F15" s="27">
+        <f>Inputs!E34+$D$5</f>
         <v>0.1206897885904732</v>
       </c>
-      <c r="G15" s="26">
-        <f>Inputs!F32+$D$5</f>
+      <c r="G15" s="27">
+        <f>Inputs!F34+$D$5</f>
         <v>0.12106417467212659</v>
       </c>
-      <c r="H15" s="26">
-        <f>Inputs!G32+$D$5</f>
+      <c r="H15" s="27">
+        <f>Inputs!G34+$D$5</f>
         <v>0.12143856075378011</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="27">
+        <v>93</v>
+      </c>
+      <c r="C16" s="28">
         <f t="shared" ref="C16:H16" si="1">C14*C15</f>
         <v>465.30640521874511</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f t="shared" si="1"/>
         <v>493.64893898326648</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f t="shared" si="1"/>
         <v>516.58202419565862</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <f t="shared" si="1"/>
         <v>533.11333213099999</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="28">
         <f t="shared" si="1"/>
         <v>542.46772368938684</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="28">
         <f t="shared" si="1"/>
         <v>544.14528326508787</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="28">
-        <f>C14*Inputs!B33</f>
+        <v>96</v>
+      </c>
+      <c r="C17" s="29">
+        <f>C14*Inputs!B35</f>
         <v>50.521415002740362</v>
       </c>
-      <c r="D17" s="28">
-        <f>D14*Inputs!C33</f>
+      <c r="D17" s="29">
+        <f>D14*Inputs!C35</f>
         <v>53.431448506898214</v>
       </c>
-      <c r="E17" s="28">
-        <f>E14*Inputs!D33</f>
+      <c r="E17" s="29">
+        <f>E14*Inputs!D35</f>
         <v>55.739687082396202</v>
       </c>
-      <c r="F17" s="28">
-        <f>F14*Inputs!E33</f>
+      <c r="F17" s="29">
+        <f>F14*Inputs!E35</f>
         <v>57.344990070369214</v>
       </c>
-      <c r="G17" s="28">
-        <f>G14*Inputs!F33</f>
+      <c r="G17" s="29">
+        <f>G14*Inputs!F35</f>
         <v>58.170757927382525</v>
       </c>
-      <c r="H17" s="28">
-        <f>H14*Inputs!G33</f>
+      <c r="H17" s="29">
+        <f>H14*Inputs!G35</f>
         <v>58.170757927382525</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="28">
+        <v>97</v>
+      </c>
+      <c r="C18" s="29">
         <f t="shared" ref="C18:H18" si="2">C16-C17</f>
         <v>414.78499021600476</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f t="shared" si="2"/>
         <v>440.21749047636825</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f t="shared" si="2"/>
         <v>460.84233711326243</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f t="shared" si="2"/>
         <v>475.7683420606308</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <f t="shared" si="2"/>
         <v>484.29696576200433</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="29">
         <f t="shared" si="2"/>
         <v>485.97452533770536</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="28">
+        <v>116</v>
+      </c>
+      <c r="C19" s="29">
         <f>-MAX(C18,0)*Inputs!$B$10</f>
         <v>-91.252697847521048</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="29">
         <f>-MAX(D18,0)*Inputs!$B$10</f>
         <v>-96.847847904801014</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="29">
         <f>-MAX(E18,0)*Inputs!$B$10</f>
         <v>-101.38531416491773</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="29">
         <f>-MAX(F18,0)*Inputs!$B$10</f>
         <v>-104.66903525333878</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="29">
         <f>-MAX(G18,0)*Inputs!$B$10</f>
         <v>-106.54533246764096</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="29">
         <f>-MAX(H18,0)*Inputs!$B$10</f>
         <v>-106.91439557429518</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="28">
+        <v>100</v>
+      </c>
+      <c r="C20" s="29">
         <f t="shared" ref="C20:H20" si="3">C18+C19</f>
         <v>323.5322923684837</v>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="29">
         <f t="shared" si="3"/>
         <v>343.36964257156723</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="29">
         <f t="shared" si="3"/>
         <v>359.45702294834473</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="29">
         <f t="shared" si="3"/>
         <v>371.09930680729201</v>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="29">
         <f t="shared" si="3"/>
         <v>377.75163329436339</v>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="29">
         <f t="shared" si="3"/>
         <v>379.06012976341015</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="28">
-        <f>-C14*Inputs!B34</f>
+        <v>101</v>
+      </c>
+      <c r="C21" s="29">
+        <f>-C14*Inputs!B36</f>
         <v>-39.779148204782338</v>
       </c>
-      <c r="D21" s="28">
-        <f>-D14*Inputs!C34</f>
+      <c r="D21" s="29">
+        <f>-D14*Inputs!C36</f>
         <v>-42.070427141377806</v>
       </c>
-      <c r="E21" s="28">
-        <f>-E14*Inputs!D34</f>
+      <c r="E21" s="29">
+        <f>-E14*Inputs!D36</f>
         <v>-43.88786959388532</v>
       </c>
-      <c r="F21" s="28">
-        <f>-F14*Inputs!E34</f>
+      <c r="F21" s="29">
+        <f>-F14*Inputs!E36</f>
         <v>-45.151840238189216</v>
       </c>
-      <c r="G21" s="28">
-        <f>-G14*Inputs!F34</f>
+      <c r="G21" s="29">
+        <f>-G14*Inputs!F36</f>
         <v>-45.802026737619137</v>
       </c>
-      <c r="H21" s="28">
-        <f>-H14*Inputs!G34</f>
+      <c r="H21" s="29">
+        <f>-H14*Inputs!G36</f>
         <v>-45.802026737619137</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="28">
-        <f>-Inputs!B35*(C14-B14)</f>
+        <v>102</v>
+      </c>
+      <c r="C22" s="29">
+        <f>-Inputs!B37*(C14-B14)</f>
         <v>-1.4442000234374965</v>
       </c>
-      <c r="D22" s="28">
-        <f>-Inputs!C35*(D14-C14)</f>
+      <c r="D22" s="29">
+        <f>-Inputs!C37*(D14-C14)</f>
         <v>15.612270937140622</v>
       </c>
-      <c r="E22" s="28">
-        <f>-Inputs!D35*(E14-D14)</f>
+      <c r="E22" s="29">
+        <f>-Inputs!D37*(E14-D14)</f>
         <v>12.383653307339882</v>
       </c>
-      <c r="F22" s="28">
-        <f>-Inputs!E35*(F14-E14)</f>
+      <c r="F22" s="29">
+        <f>-Inputs!E37*(F14-E14)</f>
         <v>8.6124180868113136</v>
       </c>
-      <c r="G22" s="28">
-        <f>-Inputs!F35*(G14-F14)</f>
+      <c r="G22" s="29">
+        <f>-Inputs!F37*(G14-F14)</f>
         <v>4.4302278638557215</v>
       </c>
-      <c r="H22" s="28">
-        <f>-Inputs!G35*(H14-G14)</f>
+      <c r="H22" s="29">
+        <f>-Inputs!G37*(H14-G14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="27">
+        <v>103</v>
+      </c>
+      <c r="C23" s="28">
         <f t="shared" ref="C23:H23" si="4">C20+C17+C21+C22</f>
         <v>332.83035914300422</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="28">
         <f t="shared" si="4"/>
         <v>370.34293487422826</v>
       </c>
-      <c r="E23" s="27">
+      <c r="E23" s="28">
         <f t="shared" si="4"/>
         <v>383.69249374419547</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="28">
         <f t="shared" si="4"/>
         <v>391.90487472628331</v>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="28">
         <f t="shared" si="4"/>
         <v>394.5505923479825</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="28">
         <f t="shared" si="4"/>
         <v>391.42886095317351</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B24" s="28">
-        <f>NPV($G$5,$C$23:$H$23)*(1+$G$5)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,$H$20*(1+$H$5)*(1-$H$5/Inputs!$B$20),$H$23*(1+$H$5))/($G$5-$H$5)/(1+$G$5)^6</f>
-        <v>5096.9907033424342</v>
+        <v>141</v>
+      </c>
+      <c r="B24" s="29">
+        <f>SUMPRODUCT($C$23:$H$23,(1+$G$5)^(-DCF!$B$6:$G$6))-$C$23*Inputs!$B$20*(1+$G$5)^(-DCF!$B$6)+IF(Inputs!$B$21=1,$H$20*(1+$H$5)*(1-$H$5/Inputs!$B$22),$H$23*(1+$H$5))/($G$5-$H$5)/(1+$G$5)^(6-Inputs!$B$19)</f>
+        <v>5258.6805223723422</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B25" s="45">
         <f>(B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>55.458239984310303</v>
+        <v>52.933293962086459</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B27" s="46" t="str">
         <f>Forecast!B4</f>
         <v>2025A</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="26">
-        <f>Inputs!B31+$C$6</f>
+      <c r="A28" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="27">
+        <f>Inputs!B33+$C$6</f>
         <v>1.47E-2</v>
       </c>
-      <c r="D28" s="26">
-        <f>Inputs!C31+$C$6</f>
+      <c r="D28" s="27">
+        <f>Inputs!C33+$C$6</f>
         <v>7.7600000000000002E-2</v>
       </c>
-      <c r="E28" s="26">
-        <f>Inputs!D31+$C$6</f>
+      <c r="E28" s="27">
+        <f>Inputs!D33+$C$6</f>
         <v>6.3200000000000006E-2</v>
       </c>
-      <c r="F28" s="26">
-        <f>Inputs!E31+$C$6</f>
+      <c r="F28" s="27">
+        <f>Inputs!E33+$C$6</f>
         <v>4.8800000000000003E-2</v>
       </c>
-      <c r="G28" s="26">
-        <f>Inputs!F31+$C$6</f>
+      <c r="G28" s="27">
+        <f>Inputs!F33+$C$6</f>
         <v>3.44E-2</v>
       </c>
-      <c r="H28" s="26">
-        <f>Inputs!G31+$C$6</f>
+      <c r="H28" s="27">
+        <f>Inputs!G33+$C$6</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" s="31">
+        <v>89</v>
+      </c>
+      <c r="B29" s="32">
         <f>Forecast!B6</f>
         <v>3912.3429999999998</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="28">
         <f t="shared" ref="C29:H29" si="5">B29*(1+C28)</f>
         <v>3969.8544420999997</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f t="shared" si="5"/>
         <v>4277.9151468069595</v>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f t="shared" si="5"/>
         <v>4548.2793840851591</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="28">
         <f t="shared" si="5"/>
         <v>4770.2354180285147</v>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="28">
         <f t="shared" si="5"/>
         <v>4934.3315164086953</v>
       </c>
-      <c r="H29" s="27">
+      <c r="H29" s="28">
         <f t="shared" si="5"/>
         <v>5033.0181467368693</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="26">
-        <f>Inputs!B32+$D$6</f>
+      <c r="A30" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="27">
+        <f>Inputs!B34+$D$6</f>
         <v>0.13456663034551269</v>
       </c>
-      <c r="D30" s="26">
-        <f>Inputs!C32+$D$6</f>
+      <c r="D30" s="27">
+        <f>Inputs!C34+$D$6</f>
         <v>0.13494101642716619</v>
       </c>
-      <c r="E30" s="26">
-        <f>Inputs!D32+$D$6</f>
+      <c r="E30" s="27">
+        <f>Inputs!D34+$D$6</f>
         <v>0.13531540250881971</v>
       </c>
-      <c r="F30" s="26">
-        <f>Inputs!E32+$D$6</f>
+      <c r="F30" s="27">
+        <f>Inputs!E34+$D$6</f>
         <v>0.1356897885904732</v>
       </c>
-      <c r="G30" s="26">
-        <f>Inputs!F32+$D$6</f>
+      <c r="G30" s="27">
+        <f>Inputs!F34+$D$6</f>
         <v>0.13606417467212659</v>
       </c>
-      <c r="H30" s="26">
-        <f>Inputs!G32+$D$6</f>
+      <c r="H30" s="27">
+        <f>Inputs!G34+$D$6</f>
         <v>0.13643856075378011</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="27">
+        <v>93</v>
+      </c>
+      <c r="C31" s="28">
         <f t="shared" ref="C31:H31" si="6">C29*C30</f>
         <v>534.20993523556217</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f t="shared" si="6"/>
         <v>577.266218099301</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f t="shared" si="6"/>
         <v>615.45225558004995</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="28">
         <f t="shared" si="6"/>
         <v>647.27223539907675</v>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="28">
         <f t="shared" si="6"/>
         <v>671.38574533881194</v>
       </c>
-      <c r="H31" s="27">
+      <c r="H31" s="28">
         <f t="shared" si="6"/>
         <v>686.69775218843608</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="28">
-        <f>C29*Inputs!B33</f>
+        <v>96</v>
+      </c>
+      <c r="C32" s="29">
+        <f>C29*Inputs!B35</f>
         <v>51.537227106947462</v>
       </c>
-      <c r="D32" s="28">
-        <f>D29*Inputs!C33</f>
+      <c r="D32" s="29">
+        <f>D29*Inputs!C35</f>
         <v>55.536515930446583</v>
       </c>
-      <c r="E32" s="28">
-        <f>E29*Inputs!D33</f>
+      <c r="E32" s="29">
+        <f>E29*Inputs!D35</f>
         <v>59.046423737250805</v>
       </c>
-      <c r="F32" s="28">
-        <f>F29*Inputs!E33</f>
+      <c r="F32" s="29">
+        <f>F29*Inputs!E35</f>
         <v>61.927889215628646</v>
       </c>
-      <c r="G32" s="28">
-        <f>G29*Inputs!F33</f>
+      <c r="G32" s="29">
+        <f>G29*Inputs!F35</f>
         <v>64.058208604646268</v>
       </c>
-      <c r="H32" s="28">
-        <f>H29*Inputs!G33</f>
+      <c r="H32" s="29">
+        <f>H29*Inputs!G35</f>
         <v>65.339372776739197</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="28">
+        <v>97</v>
+      </c>
+      <c r="C33" s="29">
         <f t="shared" ref="C33:H33" si="7">C31-C32</f>
         <v>482.67270812861472</v>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="29">
         <f t="shared" si="7"/>
         <v>521.72970216885437</v>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="29">
         <f t="shared" si="7"/>
         <v>556.4058318427991</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="29">
         <f t="shared" si="7"/>
         <v>585.34434618344812</v>
       </c>
-      <c r="G33" s="28">
+      <c r="G33" s="29">
         <f t="shared" si="7"/>
         <v>607.32753673416573</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="29">
         <f t="shared" si="7"/>
         <v>621.35837941169689</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="28">
+        <v>116</v>
+      </c>
+      <c r="C34" s="29">
         <f>-MAX(C33,0)*Inputs!$B$10</f>
         <v>-106.18799578829524</v>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="29">
         <f>-MAX(D33,0)*Inputs!$B$10</f>
         <v>-114.78053447714797</v>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="29">
         <f>-MAX(E33,0)*Inputs!$B$10</f>
         <v>-122.4092830054158</v>
       </c>
-      <c r="F34" s="28">
+      <c r="F34" s="29">
         <f>-MAX(F33,0)*Inputs!$B$10</f>
         <v>-128.77575616035858</v>
       </c>
-      <c r="G34" s="28">
+      <c r="G34" s="29">
         <f>-MAX(G33,0)*Inputs!$B$10</f>
         <v>-133.61205808151647</v>
       </c>
-      <c r="H34" s="28">
+      <c r="H34" s="29">
         <f>-MAX(H33,0)*Inputs!$B$10</f>
         <v>-136.69884347057331</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="28">
+        <v>100</v>
+      </c>
+      <c r="C35" s="29">
         <f t="shared" ref="C35:H35" si="8">C33+C34</f>
         <v>376.48471234031945</v>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="29">
         <f t="shared" si="8"/>
         <v>406.94916769170641</v>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="29">
         <f t="shared" si="8"/>
         <v>433.99654883738333</v>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="29">
         <f t="shared" si="8"/>
         <v>456.56859002308954</v>
       </c>
-      <c r="G35" s="28">
+      <c r="G35" s="29">
         <f t="shared" si="8"/>
         <v>473.71547865264927</v>
       </c>
-      <c r="H35" s="28">
+      <c r="H35" s="29">
         <f t="shared" si="8"/>
         <v>484.65953594112358</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="28">
-        <f>-C29*Inputs!B34</f>
+        <v>101</v>
+      </c>
+      <c r="C36" s="29">
+        <f>-C29*Inputs!B36</f>
         <v>-40.578970225588257</v>
       </c>
-      <c r="D36" s="28">
-        <f>-D29*Inputs!C34</f>
+      <c r="D36" s="29">
+        <f>-D29*Inputs!C36</f>
         <v>-43.727898315093903</v>
       </c>
-      <c r="E36" s="28">
-        <f>-E29*Inputs!D34</f>
+      <c r="E36" s="29">
+        <f>-E29*Inputs!D36</f>
         <v>-46.491501488607838</v>
       </c>
-      <c r="F36" s="28">
-        <f>-F29*Inputs!E34</f>
+      <c r="F36" s="29">
+        <f>-F29*Inputs!E36</f>
         <v>-48.760286761251898</v>
       </c>
-      <c r="G36" s="28">
-        <f>-G29*Inputs!F34</f>
+      <c r="G36" s="29">
+        <f>-G29*Inputs!F36</f>
         <v>-50.437640625838959</v>
       </c>
-      <c r="H36" s="28">
-        <f>-H29*Inputs!G34</f>
+      <c r="H36" s="29">
+        <f>-H29*Inputs!G36</f>
         <v>-51.446393438355734</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="28">
-        <f>-Inputs!B35*(C29-B29)</f>
+        <v>102</v>
+      </c>
+      <c r="C37" s="29">
+        <f>-Inputs!B37*(C29-B29)</f>
         <v>4.005611385760611</v>
       </c>
-      <c r="D37" s="28">
-        <f>-Inputs!C35*(D29-C29)</f>
+      <c r="D37" s="29">
+        <f>-Inputs!C37*(D29-C29)</f>
         <v>21.456103711223736</v>
       </c>
-      <c r="E37" s="28">
-        <f>-Inputs!D35*(E29-D29)</f>
+      <c r="E37" s="29">
+        <f>-Inputs!D37*(E29-D29)</f>
         <v>18.830584447195474</v>
       </c>
-      <c r="F37" s="28">
-        <f>-Inputs!E35*(F29-E29)</f>
+      <c r="F37" s="29">
+        <f>-Inputs!E37*(F29-E29)</f>
         <v>15.459004056199388</v>
       </c>
-      <c r="G37" s="28">
-        <f>-Inputs!F35*(G29-F29)</f>
+      <c r="G37" s="29">
+        <f>-Inputs!F37*(G29-F29)</f>
         <v>11.429120467673799</v>
       </c>
-      <c r="H37" s="28">
-        <f>-Inputs!G35*(H29-G29)</f>
+      <c r="H37" s="29">
+        <f>-Inputs!G37*(H29-G29)</f>
         <v>6.8734198905591946</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" s="27">
+        <v>103</v>
+      </c>
+      <c r="C38" s="28">
         <f t="shared" ref="C38:H38" si="9">C35+C32+C36+C37</f>
         <v>391.44858060743928</v>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="28">
         <f t="shared" si="9"/>
         <v>440.21388901828283</v>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="28">
         <f t="shared" si="9"/>
         <v>465.38205553322172</v>
       </c>
-      <c r="F38" s="27">
+      <c r="F38" s="28">
         <f t="shared" si="9"/>
         <v>485.19519653366564</v>
       </c>
-      <c r="G38" s="27">
+      <c r="G38" s="28">
         <f t="shared" si="9"/>
         <v>498.76516709913028</v>
       </c>
-      <c r="H38" s="27">
+      <c r="H38" s="28">
         <f t="shared" si="9"/>
         <v>505.42593517006628</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B39" s="28">
-        <f>NPV($G$6,$C$38:$H$38)*(1+$G$6)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,$H$35*(1+$H$6)*(1-$H$6/Inputs!$B$20),$H$38*(1+$H$6))/($G$6-$H$6)/(1+$G$6)^6</f>
-        <v>7175.4832253619898</v>
+        <v>141</v>
+      </c>
+      <c r="B39" s="29">
+        <f>SUMPRODUCT($C$38:$H$38,(1+$G$6)^(-DCF!$B$6:$G$6))-$C$38*Inputs!$B$20*(1+$G$6)^(-DCF!$B$6)+IF(Inputs!$B$21=1,$H$35*(1+$H$6)*(1-$H$6/Inputs!$B$22),$H$38*(1+$H$6))/($G$6-$H$6)/(1+$G$6)^(6-Inputs!$B$19)</f>
+        <v>7414.6626807800012</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B40" s="45">
         <f>(B39-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>75.763345013999682</v>
+        <v>73.995406865946137</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B42" s="46" t="str">
         <f>Forecast!B4</f>
         <v>2025A</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="26">
-        <f>Inputs!B31+$C$7</f>
+      <c r="A43" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="27">
+        <f>Inputs!B33+$C$7</f>
         <v>3.4700000000000002E-2</v>
       </c>
-      <c r="D43" s="26">
-        <f>Inputs!C31+$C$7</f>
+      <c r="D43" s="27">
+        <f>Inputs!C33+$C$7</f>
         <v>9.7600000000000006E-2</v>
       </c>
-      <c r="E43" s="26">
-        <f>Inputs!D31+$C$7</f>
+      <c r="E43" s="27">
+        <f>Inputs!D33+$C$7</f>
         <v>8.320000000000001E-2</v>
       </c>
-      <c r="F43" s="26">
-        <f>Inputs!E31+$C$7</f>
+      <c r="F43" s="27">
+        <f>Inputs!E33+$C$7</f>
         <v>6.88E-2</v>
       </c>
-      <c r="G43" s="26">
-        <f>Inputs!F31+$C$7</f>
+      <c r="G43" s="27">
+        <f>Inputs!F33+$C$7</f>
         <v>5.4400000000000004E-2</v>
       </c>
-      <c r="H43" s="26">
-        <f>Inputs!G31+$C$7</f>
+      <c r="H43" s="27">
+        <f>Inputs!G33+$C$7</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="31">
+        <v>89</v>
+      </c>
+      <c r="B44" s="32">
         <f>Forecast!B6</f>
         <v>3912.3429999999998</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="28">
         <f t="shared" ref="C44:H44" si="10">B44*(1+C43)</f>
         <v>4048.1013020999999</v>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="28">
         <f t="shared" si="10"/>
         <v>4443.1959891849592</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="28">
         <f t="shared" si="10"/>
         <v>4812.8698954851479</v>
       </c>
-      <c r="F44" s="27">
+      <c r="F44" s="28">
         <f t="shared" si="10"/>
         <v>5143.9953442945261</v>
       </c>
-      <c r="G44" s="27">
+      <c r="G44" s="28">
         <f t="shared" si="10"/>
         <v>5423.8286910241486</v>
       </c>
-      <c r="H44" s="27">
+      <c r="H44" s="28">
         <f t="shared" si="10"/>
         <v>5640.7818386651152</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="26">
-        <f>Inputs!B32+$D$7</f>
+      <c r="A45" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C45" s="27">
+        <f>Inputs!B34+$D$7</f>
         <v>0.14956663034551271</v>
       </c>
-      <c r="D45" s="26">
-        <f>Inputs!C32+$D$7</f>
+      <c r="D45" s="27">
+        <f>Inputs!C34+$D$7</f>
         <v>0.14994101642716617</v>
       </c>
-      <c r="E45" s="26">
-        <f>Inputs!D32+$D$7</f>
+      <c r="E45" s="27">
+        <f>Inputs!D34+$D$7</f>
         <v>0.1503154025088197</v>
       </c>
-      <c r="F45" s="26">
-        <f>Inputs!E32+$D$7</f>
+      <c r="F45" s="27">
+        <f>Inputs!E34+$D$7</f>
         <v>0.15068978859047322</v>
       </c>
-      <c r="G45" s="26">
-        <f>Inputs!F32+$D$7</f>
+      <c r="G45" s="27">
+        <f>Inputs!F34+$D$7</f>
         <v>0.15106417467212657</v>
       </c>
-      <c r="H45" s="26">
-        <f>Inputs!G32+$D$7</f>
+      <c r="H45" s="27">
+        <f>Inputs!G34+$D$7</f>
         <v>0.15143856075378009</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="27">
+        <v>93</v>
+      </c>
+      <c r="C46" s="28">
         <f t="shared" ref="C46:H46" si="11">C44*C45</f>
         <v>605.46087105237939</v>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="28">
         <f t="shared" si="11"/>
         <v>666.21732280350079</v>
       </c>
-      <c r="E46" s="27">
+      <c r="E46" s="28">
         <f t="shared" si="11"/>
         <v>723.44847556243099</v>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="28">
         <f t="shared" si="11"/>
         <v>775.14757094212064</v>
       </c>
-      <c r="G46" s="27">
+      <c r="G46" s="28">
         <f t="shared" si="11"/>
         <v>819.34620477256362</v>
       </c>
-      <c r="H46" s="27">
+      <c r="H46" s="28">
         <f t="shared" si="11"/>
         <v>854.23188317350639</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="28">
-        <f>C44*Inputs!B33</f>
+        <v>96</v>
+      </c>
+      <c r="C47" s="29">
+        <f>C44*Inputs!B35</f>
         <v>52.553039211154569</v>
       </c>
-      <c r="D47" s="28">
-        <f>D44*Inputs!C33</f>
+      <c r="D47" s="29">
+        <f>D44*Inputs!C35</f>
         <v>57.682215838163252</v>
       </c>
-      <c r="E47" s="28">
-        <f>E44*Inputs!D33</f>
+      <c r="E47" s="29">
+        <f>E44*Inputs!D35</f>
         <v>62.481376195898434</v>
       </c>
-      <c r="F47" s="28">
-        <f>F44*Inputs!E33</f>
+      <c r="F47" s="29">
+        <f>F44*Inputs!E35</f>
         <v>66.780094878176243</v>
       </c>
-      <c r="G47" s="28">
-        <f>G44*Inputs!F33</f>
+      <c r="G47" s="29">
+        <f>G44*Inputs!F35</f>
         <v>70.412932039549034</v>
       </c>
-      <c r="H47" s="28">
-        <f>H44*Inputs!G33</f>
+      <c r="H47" s="29">
+        <f>H44*Inputs!G35</f>
         <v>73.229449321131</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" s="28">
+        <v>97</v>
+      </c>
+      <c r="C48" s="29">
         <f t="shared" ref="C48:H48" si="12">C46-C47</f>
         <v>552.90783184122483</v>
       </c>
-      <c r="D48" s="28">
+      <c r="D48" s="29">
         <f t="shared" si="12"/>
         <v>608.53510696533749</v>
       </c>
-      <c r="E48" s="28">
+      <c r="E48" s="29">
         <f t="shared" si="12"/>
         <v>660.96709936653258</v>
       </c>
-      <c r="F48" s="28">
+      <c r="F48" s="29">
         <f t="shared" si="12"/>
         <v>708.36747606394442</v>
       </c>
-      <c r="G48" s="28">
+      <c r="G48" s="29">
         <f t="shared" si="12"/>
         <v>748.93327273301463</v>
       </c>
-      <c r="H48" s="28">
+      <c r="H48" s="29">
         <f t="shared" si="12"/>
         <v>781.00243385237536</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" s="28">
+        <v>116</v>
+      </c>
+      <c r="C49" s="29">
         <f>-MAX(C48,0)*Inputs!$B$10</f>
         <v>-121.63972300506947</v>
       </c>
-      <c r="D49" s="28">
+      <c r="D49" s="29">
         <f>-MAX(D48,0)*Inputs!$B$10</f>
         <v>-133.87772353237426</v>
       </c>
-      <c r="E49" s="28">
+      <c r="E49" s="29">
         <f>-MAX(E48,0)*Inputs!$B$10</f>
         <v>-145.41276186063718</v>
       </c>
-      <c r="F49" s="28">
+      <c r="F49" s="29">
         <f>-MAX(F48,0)*Inputs!$B$10</f>
         <v>-155.84084473406779</v>
       </c>
-      <c r="G49" s="28">
+      <c r="G49" s="29">
         <f>-MAX(G48,0)*Inputs!$B$10</f>
         <v>-164.76532000126323</v>
       </c>
-      <c r="H49" s="28">
+      <c r="H49" s="29">
         <f>-MAX(H48,0)*Inputs!$B$10</f>
         <v>-171.82053544752259</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C50" s="28">
+        <v>100</v>
+      </c>
+      <c r="C50" s="29">
         <f t="shared" ref="C50:H50" si="13">C48+C49</f>
         <v>431.26810883615536</v>
       </c>
-      <c r="D50" s="28">
+      <c r="D50" s="29">
         <f t="shared" si="13"/>
         <v>474.65738343296323</v>
       </c>
-      <c r="E50" s="28">
+      <c r="E50" s="29">
         <f t="shared" si="13"/>
         <v>515.55433750589543</v>
       </c>
-      <c r="F50" s="28">
+      <c r="F50" s="29">
         <f t="shared" si="13"/>
         <v>552.52663132987664</v>
       </c>
-      <c r="G50" s="28">
+      <c r="G50" s="29">
         <f t="shared" si="13"/>
         <v>584.16795273175137</v>
       </c>
-      <c r="H50" s="28">
+      <c r="H50" s="29">
         <f t="shared" si="13"/>
         <v>609.18189840485275</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" s="28">
-        <f>-C44*Inputs!B34</f>
+        <v>101</v>
+      </c>
+      <c r="C51" s="29">
+        <f>-C44*Inputs!B36</f>
         <v>-41.378792246394177</v>
       </c>
-      <c r="D51" s="28">
-        <f>-D44*Inputs!C34</f>
+      <c r="D51" s="29">
+        <f>-D44*Inputs!C36</f>
         <v>-45.417362369642241</v>
       </c>
-      <c r="E51" s="28">
-        <f>-E44*Inputs!D34</f>
+      <c r="E51" s="29">
+        <f>-E44*Inputs!D36</f>
         <v>-49.196086918796475</v>
       </c>
-      <c r="F51" s="28">
-        <f>-F44*Inputs!E34</f>
+      <c r="F51" s="29">
+        <f>-F44*Inputs!E36</f>
         <v>-52.580777698809676</v>
       </c>
-      <c r="G51" s="28">
-        <f>-G44*Inputs!F34</f>
+      <c r="G51" s="29">
+        <f>-G44*Inputs!F36</f>
         <v>-55.441172005624921</v>
       </c>
-      <c r="H51" s="28">
-        <f>-H44*Inputs!G34</f>
+      <c r="H51" s="29">
+        <f>-H44*Inputs!G36</f>
         <v>-57.658818885849925</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="28">
-        <f>-Inputs!B35*(C44-B44)</f>
+        <v>102</v>
+      </c>
+      <c r="C52" s="29">
+        <f>-Inputs!B37*(C44-B44)</f>
         <v>9.4554227949587517</v>
       </c>
-      <c r="D52" s="28">
-        <f>-Inputs!C35*(D44-C44)</f>
+      <c r="D52" s="29">
+        <f>-Inputs!C37*(D44-C44)</f>
         <v>27.517928941674782</v>
       </c>
-      <c r="E52" s="28">
-        <f>-Inputs!D35*(E44-D44)</f>
+      <c r="E52" s="29">
+        <f>-Inputs!D37*(E44-D44)</f>
         <v>25.747398326752119</v>
       </c>
-      <c r="F52" s="28">
-        <f>-Inputs!E35*(F44-E44)</f>
+      <c r="F52" s="29">
+        <f>-Inputs!E37*(F44-E44)</f>
         <v>23.062538852002486</v>
       </c>
-      <c r="G52" s="28">
-        <f>-Inputs!F35*(G44-F44)</f>
+      <c r="G52" s="29">
+        <f>-Inputs!F37*(G44-F44)</f>
         <v>19.490097950016033</v>
       </c>
-      <c r="H52" s="28">
-        <f>-Inputs!G35*(H44-G44)</f>
+      <c r="H52" s="29">
+        <f>-Inputs!G37*(H44-G44)</f>
         <v>15.110558293012462</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="27">
+        <v>103</v>
+      </c>
+      <c r="C53" s="28">
         <f t="shared" ref="C53:H53" si="14">C50+C47+C51+C52</f>
         <v>451.89777859587446</v>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="28">
         <f t="shared" si="14"/>
         <v>514.44016584315909</v>
       </c>
-      <c r="E53" s="27">
+      <c r="E53" s="28">
         <f t="shared" si="14"/>
         <v>554.58702510974945</v>
       </c>
-      <c r="F53" s="27">
+      <c r="F53" s="28">
         <f t="shared" si="14"/>
         <v>589.78848736124564</v>
       </c>
-      <c r="G53" s="27">
+      <c r="G53" s="28">
         <f t="shared" si="14"/>
         <v>618.62981071569141</v>
       </c>
-      <c r="H53" s="27">
+      <c r="H53" s="28">
         <f t="shared" si="14"/>
         <v>639.86308713314634</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="28">
-        <f>NPV($G$7,$C$53:$H$53)*(1+$G$7)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,$H$50*(1+$H$7)*(1-$H$7/Inputs!$B$20),$H$53*(1+$H$7))/($G$7-$H$7)/(1+$G$7)^6</f>
-        <v>10085.824930021969</v>
+        <v>141</v>
+      </c>
+      <c r="B54" s="29">
+        <f>SUMPRODUCT($C$53:$H$53,(1+$G$7)^(-DCF!$B$6:$G$6))-$C$53*Inputs!$B$20*(1+$G$7)^(-DCF!$B$6)+IF(Inputs!$B$21=1,$H$50*(1+$H$7)*(1-$H$7/Inputs!$B$22),$H$53*(1+$H$7))/($G$7-$H$7)/(1+$G$7)^(6-Inputs!$B$19)</f>
+        <v>10433.455856800214</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B55" s="45">
         <f>(B54-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>104.19490940951984</v>
+        <v>103.48644994289751</v>
       </c>
     </row>
   </sheetData>
@@ -5572,227 +5743,360 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="12" width="12" customWidth="1"/>
+    <col min="6" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="T4" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="U4" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D5" s="18">
-        <v>2496.8972178954768</v>
+        <v>2423.17509200528</v>
       </c>
       <c r="E5" s="18">
-        <v>2501.118472354859</v>
+        <v>2924.2344559307371</v>
       </c>
       <c r="F5" s="19">
         <v>-9.6288598796959501E-2</v>
       </c>
       <c r="G5" s="19">
-        <v>8.7888884078785354E-2</v>
+        <v>8.6789313082291486E-2</v>
       </c>
       <c r="H5" s="47">
-        <v>0.45127887932023242</v>
+        <v>0.54439622939171328</v>
       </c>
       <c r="I5" s="47">
-        <v>5.1346525109557302</v>
+        <v>6.2726182528432988</v>
       </c>
       <c r="J5" s="47"/>
       <c r="K5" s="47"/>
       <c r="L5" s="47">
-        <v>9.2567570000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>13.18452357388545</v>
+      </c>
+      <c r="M5" s="47">
+        <v>0.51878364242310715</v>
+      </c>
+      <c r="N5" s="47">
+        <v>5.9775060315457189</v>
+      </c>
+      <c r="O5" s="47">
+        <v>14.79552016547999</v>
+      </c>
+      <c r="P5" s="47">
+        <v>12.671499242033841</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>4.7581535303245381E-2</v>
+      </c>
+      <c r="R5" s="19">
+        <v>0.16762191141521471</v>
+      </c>
+      <c r="S5" s="24">
+        <v>0.78656325193823817</v>
+      </c>
+      <c r="T5" s="19">
+        <v>0.120918609684653</v>
+      </c>
+      <c r="U5" s="19">
+        <v>2.696871628910464E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D6" s="18">
-        <v>22628.104704038818</v>
+        <v>22273.99931079102</v>
       </c>
       <c r="E6" s="18">
-        <v>28050.965804617132</v>
+        <v>25742.59536391449</v>
       </c>
       <c r="F6" s="19">
         <v>-1.447193402500668E-2</v>
       </c>
       <c r="G6" s="19">
-        <v>0.1761155050477784</v>
+        <v>0.18549722597226831</v>
       </c>
       <c r="H6" s="47">
-        <v>1.4038376850402201</v>
+        <v>1.325569780850945</v>
       </c>
       <c r="I6" s="47">
-        <v>7.9711192075869333</v>
+        <v>7.1460356018969096</v>
       </c>
       <c r="J6" s="47">
-        <v>37.169454056854931</v>
+        <v>7.8935247953885739</v>
       </c>
       <c r="K6" s="47">
-        <v>10.068784000000001</v>
+        <v>9.8730150000000005</v>
       </c>
       <c r="L6" s="47">
-        <v>11.440906</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>11.371885710510099</v>
+      </c>
+      <c r="M6" s="47">
+        <v>1.355844972713381</v>
+      </c>
+      <c r="N6" s="47">
+        <v>7.3092466240766241</v>
+      </c>
+      <c r="O6" s="47">
+        <v>11.772870662460569</v>
+      </c>
+      <c r="P6" s="47">
+        <v>11.229666540287781</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>6.3180840432657259E-3</v>
+      </c>
+      <c r="R6" s="19">
+        <v>4.8372239747634049E-2</v>
+      </c>
+      <c r="S6" s="24">
+        <v>2.3509115496489521</v>
+      </c>
+      <c r="T6" s="19">
+        <v>8.7152926959923577E-2</v>
+      </c>
+      <c r="U6" s="19">
+        <v>4.7159699892818867E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D7" s="18">
-        <v>20082.090670988771</v>
+        <v>20420.670457042968</v>
       </c>
       <c r="E7" s="18">
-        <v>23434.787189886782</v>
+        <v>25026.702571071899</v>
       </c>
       <c r="F7" s="19">
         <v>0.2065712625752989</v>
       </c>
       <c r="G7" s="19">
-        <v>8.8841314292231077E-2</v>
+        <v>9.8755532726564454E-2</v>
       </c>
       <c r="H7" s="47">
-        <v>2.0601835427094288</v>
+        <v>1.858554844368014</v>
       </c>
       <c r="I7" s="47">
-        <v>23.189476192717539</v>
+        <v>18.819754124703099</v>
       </c>
       <c r="J7" s="47">
-        <v>36.104875683142019</v>
+        <v>26.576875769314491</v>
       </c>
       <c r="K7" s="47">
-        <v>34.457832000000003</v>
+        <v>34.895947</v>
       </c>
       <c r="L7" s="47">
-        <v>13.325583999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14.550300473379769</v>
+      </c>
+      <c r="M7" s="47">
+        <v>1.705353249890301</v>
+      </c>
+      <c r="N7" s="47">
+        <v>17.268432489874812</v>
+      </c>
+      <c r="O7" s="47">
+        <v>18.425237833617679</v>
+      </c>
+      <c r="P7" s="47">
+        <v>13.49501370679986</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>7.9394535382392384E-2</v>
+      </c>
+      <c r="R7" s="19">
+        <v>0.36533672613711959</v>
+      </c>
+      <c r="S7" s="24">
+        <v>0.39827094930277263</v>
+      </c>
+      <c r="T7" s="19">
+        <v>1.26085312889661E-2</v>
+      </c>
+      <c r="U7" s="19"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D8" s="18">
-        <v>18898.264063999999</v>
+        <v>19121.383424</v>
       </c>
       <c r="E8" s="18">
-        <v>17896.264063999999</v>
+        <v>20385.383424</v>
       </c>
       <c r="F8" s="19">
         <v>8.0918503094453031E-2</v>
       </c>
       <c r="G8" s="19">
-        <v>4.2940188891267127E-2</v>
+        <v>4.7867959455448042E-2</v>
       </c>
       <c r="H8" s="47">
-        <v>0.47881699657534249</v>
+        <v>0.51269795588642142</v>
       </c>
       <c r="I8" s="47">
-        <v>11.150789247522869</v>
+        <v>10.710670806086959</v>
       </c>
       <c r="J8" s="47">
-        <v>14.31778441155822</v>
+        <v>12.940358047160901</v>
       </c>
       <c r="K8" s="47">
-        <v>16.494644000000001</v>
+        <v>16.673151000000001</v>
       </c>
       <c r="L8" s="47">
-        <v>14.611848999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>15.186763460925629</v>
+      </c>
+      <c r="M8" s="47">
+        <v>0.48169418006588388</v>
+      </c>
+      <c r="N8" s="47">
+        <v>10.062977105055189</v>
+      </c>
+      <c r="O8" s="47">
+        <v>16.38623326959847</v>
+      </c>
+      <c r="P8" s="47">
+        <v>14.78436307773522</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>3.4908327356433233E-2</v>
+      </c>
+      <c r="R8" s="19">
+        <v>0.10834894837476081</v>
+      </c>
+      <c r="S8" s="24">
+        <v>1.401653056049714</v>
+      </c>
+      <c r="T8" s="19">
+        <v>1.8199519997240971E-2</v>
+      </c>
+      <c r="U8" s="19">
+        <v>4.3757292882147032E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D9" s="18">
-        <v>34043.29139832715</v>
+        <v>33798.316674377442</v>
       </c>
       <c r="E9" s="18">
-        <v>37341.020935718807</v>
+        <v>41167.594270851143</v>
       </c>
       <c r="F9" s="19">
         <v>-2.2296080875225052E-2</v>
@@ -5801,36 +6105,63 @@
         <v>8.8277576133144478E-2</v>
       </c>
       <c r="H9" s="47">
-        <v>0.61287499716713878</v>
+        <v>0.6730758583569405</v>
       </c>
       <c r="I9" s="47">
-        <v>6.9425897720930996</v>
+        <v>7.6245394112517904</v>
       </c>
       <c r="J9" s="47">
-        <v>8.0558167197764448</v>
+        <v>8.8471152820597556</v>
       </c>
       <c r="K9" s="47">
-        <v>10.515131999999999</v>
+        <v>10.392535000000001</v>
       </c>
       <c r="L9" s="47">
-        <v>8.1492020000000007</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>8.2712229695430626</v>
+      </c>
+      <c r="M9" s="47">
+        <v>0.63167461181612539</v>
+      </c>
+      <c r="N9" s="47">
+        <v>7.1555500217111012</v>
+      </c>
+      <c r="O9" s="47">
+        <v>8.9004156466551532</v>
+      </c>
+      <c r="P9" s="47">
+        <v>8.0593768978834532</v>
+      </c>
+      <c r="Q9" s="19">
+        <v>3.8130922375308351E-2</v>
+      </c>
+      <c r="R9" s="19">
+        <v>0.104355306797052</v>
+      </c>
+      <c r="S9" s="24">
+        <v>0.79260204616414631</v>
+      </c>
+      <c r="T9" s="19">
+        <v>0.11749317128535031</v>
+      </c>
+      <c r="U9" s="19">
+        <v>3.2817337461300312E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D10" s="18">
-        <v>189192.09216649219</v>
+        <v>191092.62304101561</v>
       </c>
       <c r="E10" s="18">
-        <v>249040.9749713628</v>
+        <v>264752.91137490852</v>
       </c>
       <c r="F10" s="19">
         <v>1.6699855177407571E-2</v>
@@ -5839,377 +6170,694 @@
         <v>0.121202203427554</v>
       </c>
       <c r="H10" s="47">
-        <v>1.027648965768974</v>
+        <v>1.0882721987091031</v>
       </c>
       <c r="I10" s="47">
-        <v>8.4787977174295275</v>
+        <v>8.9789803149873801</v>
       </c>
       <c r="J10" s="47">
-        <v>9.947457518988541</v>
+        <v>10.534279531585449</v>
       </c>
       <c r="K10" s="47">
-        <v>13.4243965</v>
+        <v>13.5069895</v>
       </c>
       <c r="L10" s="47">
-        <v>7.7001679999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>7.909356795016012</v>
+      </c>
+      <c r="M10" s="47">
+        <v>0.9760646897368862</v>
+      </c>
+      <c r="N10" s="47">
+        <v>8.0531926164222583</v>
+      </c>
+      <c r="O10" s="47">
+        <v>8.3800688379690431</v>
+      </c>
+      <c r="P10" s="47">
+        <v>7.7475423600340507</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>4.2978720542340199E-2</v>
+      </c>
+      <c r="R10" s="19">
+        <v>8.1642209689346101E-2</v>
+      </c>
+      <c r="S10" s="24">
+        <v>0.96878279325261119</v>
+      </c>
+      <c r="T10" s="19">
+        <v>0.1076162438772512</v>
+      </c>
+      <c r="U10" s="19">
+        <v>3.1984948259642522E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="D11" s="18">
-        <v>44792.999249311521</v>
+        <v>46697.301268310548</v>
       </c>
       <c r="E11" s="18">
-        <v>39143.428682073667</v>
+        <v>41599.2447733593</v>
       </c>
       <c r="F11" s="19">
         <v>6.7098066236980225E-2</v>
       </c>
       <c r="G11" s="19">
-        <v>0.17411845084328881</v>
+        <v>0.16828794626163299</v>
       </c>
       <c r="H11" s="47">
-        <v>1.481067252900113</v>
+        <v>1.520311471737601</v>
       </c>
       <c r="I11" s="47">
-        <v>8.5060902260904694</v>
+        <v>9.033989097317825</v>
       </c>
       <c r="J11" s="47">
-        <v>9.7174560004333035</v>
+        <v>9.8478415822794432</v>
       </c>
       <c r="K11" s="47">
-        <v>16.375359</v>
+        <v>17.00573</v>
       </c>
       <c r="L11" s="47">
-        <v>13.736793</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14.561277499330091</v>
+      </c>
+      <c r="M11" s="47">
+        <v>1.340231092458414</v>
+      </c>
+      <c r="N11" s="47">
+        <v>7.9639161462864978</v>
+      </c>
+      <c r="O11" s="47">
+        <v>15.42089160555256</v>
+      </c>
+      <c r="P11" s="47">
+        <v>14.26559240065764</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>7.9588733768499287E-2</v>
+      </c>
+      <c r="R11" s="19">
+        <v>8.0985014323111226E-2</v>
+      </c>
+      <c r="S11" s="24">
+        <v>1.7980212291170321</v>
+      </c>
+      <c r="T11" s="19">
+        <v>5.6571399852651152E-2</v>
+      </c>
+      <c r="U11" s="19">
+        <v>1.13732097725358E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="D12" s="18">
-        <v>1090732.5412987501</v>
+        <v>1067187.5548550941</v>
       </c>
       <c r="E12" s="18">
-        <v>1041316.189605029</v>
+        <v>1035029.714072497</v>
       </c>
       <c r="F12" s="19">
         <v>7.3602053264412159E-2</v>
       </c>
       <c r="G12" s="19">
-        <v>0.16834948989620471</v>
+        <v>0.16670189772912311</v>
       </c>
       <c r="H12" s="47">
-        <v>1.598291522981715</v>
+        <v>1.499575631853612</v>
       </c>
       <c r="I12" s="47">
-        <v>9.4938899070447818</v>
+        <v>8.995552253941943</v>
       </c>
       <c r="J12" s="47">
-        <v>10.74775198806914</v>
+        <v>10.177790463860751</v>
       </c>
       <c r="K12" s="47">
-        <v>15.236610000000001</v>
+        <v>14.740622500000001</v>
       </c>
       <c r="L12" s="47">
-        <v>12.987819</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>12.585516094742291</v>
+      </c>
+      <c r="M12" s="47">
+        <v>1.431885547288364</v>
+      </c>
+      <c r="N12" s="47">
+        <v>8.5894975809757188</v>
+      </c>
+      <c r="O12" s="47">
+        <v>13.32027508856144</v>
+      </c>
+      <c r="P12" s="47">
+        <v>12.585516094742291</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>4.0655461543369187E-2</v>
+      </c>
+      <c r="R12" s="19">
+        <v>5.8381316132605443E-2</v>
+      </c>
+      <c r="S12" s="24">
+        <v>2.15574381128304</v>
+      </c>
+      <c r="T12" s="19">
+        <v>9.6211389279712234E-2</v>
+      </c>
+      <c r="U12" s="19">
+        <v>3.5300487276664863E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="F14" s="48">
-        <f t="shared" ref="F14:L14" si="0">IFERROR(AVERAGE(F5:F12),"")</f>
+        <f t="shared" ref="F14:U14" si="0">IFERROR(AVERAGE(F5:F12),"")</f>
         <v>3.8979140831420081E-2</v>
       </c>
       <c r="G14" s="48">
         <f t="shared" si="0"/>
-        <v>0.11846670157628174</v>
+        <v>0.12042245684850336</v>
       </c>
       <c r="H14" s="49">
         <f t="shared" si="0"/>
-        <v>1.1392499803078955</v>
+        <v>1.1278067463942938</v>
       </c>
       <c r="I14" s="49">
         <f t="shared" si="0"/>
-        <v>10.108425597680117</v>
+        <v>9.6977674828786498</v>
       </c>
       <c r="J14" s="49">
         <f t="shared" si="0"/>
-        <v>18.008656625546084</v>
+        <v>12.402540781664195</v>
       </c>
       <c r="K14" s="49">
         <f t="shared" si="0"/>
-        <v>16.653251071428574</v>
+        <v>16.726855714285715</v>
       </c>
       <c r="L14" s="49">
         <f t="shared" si="0"/>
-        <v>11.401134750000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>12.20260582216655</v>
+      </c>
+      <c r="M14" s="49">
+        <f t="shared" si="0"/>
+        <v>1.0551914982990578</v>
+      </c>
+      <c r="N14" s="49">
+        <f t="shared" si="0"/>
+        <v>9.047539826993491</v>
+      </c>
+      <c r="O14" s="49">
+        <f t="shared" si="0"/>
+        <v>13.425189138736863</v>
+      </c>
+      <c r="P14" s="49">
+        <f t="shared" si="0"/>
+        <v>11.854821290021766</v>
+      </c>
+      <c r="Q14" s="48">
+        <f t="shared" si="0"/>
+        <v>4.6194540039356718E-2</v>
+      </c>
+      <c r="R14" s="48">
+        <f t="shared" si="0"/>
+        <v>0.12688045907710549</v>
+      </c>
+      <c r="S14" s="50">
+        <f t="shared" si="0"/>
+        <v>1.3315685858445632</v>
+      </c>
+      <c r="T14" s="48">
+        <f t="shared" si="0"/>
+        <v>7.7096474028218565E-2</v>
+      </c>
+      <c r="U14" s="48">
+        <f t="shared" si="0"/>
+        <v>3.2765955976316284E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="F15" s="40">
-        <f t="shared" ref="F15:L15" si="1">IFERROR(MEDIAN(F5:F12),"")</f>
+        <f t="shared" ref="F15:U15" si="1">IFERROR(MEDIAN(F5:F12),"")</f>
         <v>4.18989607071939E-2</v>
       </c>
       <c r="G15" s="40">
         <f t="shared" si="1"/>
-        <v>0.10502175885989254</v>
-      </c>
-      <c r="H15" s="50">
+        <v>0.10997886807705923</v>
+      </c>
+      <c r="H15" s="51">
         <f t="shared" si="1"/>
-        <v>1.2157433254045971</v>
-      </c>
-      <c r="I15" s="50">
+        <v>1.2069209897800239</v>
+      </c>
+      <c r="I15" s="51">
         <f t="shared" si="1"/>
-        <v>8.4924439717599984</v>
-      </c>
-      <c r="J15" s="50">
+        <v>8.9872662844646616</v>
+      </c>
+      <c r="J15" s="51">
         <f t="shared" si="1"/>
-        <v>10.74775198806914</v>
-      </c>
-      <c r="K15" s="50">
+        <v>10.177790463860751</v>
+      </c>
+      <c r="K15" s="51">
         <f t="shared" si="1"/>
-        <v>15.236610000000001</v>
-      </c>
-      <c r="L15" s="50">
+        <v>14.740622500000001</v>
+      </c>
+      <c r="L15" s="51">
         <f t="shared" si="1"/>
-        <v>12.2143625</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>12.885019834313869</v>
+      </c>
+      <c r="M15" s="51">
+        <f t="shared" si="1"/>
+        <v>1.1581478910976502</v>
+      </c>
+      <c r="N15" s="51">
+        <f t="shared" si="1"/>
+        <v>8.0085543813543776</v>
+      </c>
+      <c r="O15" s="51">
+        <f t="shared" si="1"/>
+        <v>14.057897627020715</v>
+      </c>
+      <c r="P15" s="51">
+        <f t="shared" si="1"/>
+        <v>12.628507668388066</v>
+      </c>
+      <c r="Q15" s="40">
+        <f t="shared" si="1"/>
+        <v>4.1817091042854693E-2</v>
+      </c>
+      <c r="R15" s="40">
+        <f t="shared" si="1"/>
+        <v>9.2998758243199059E-2</v>
+      </c>
+      <c r="S15" s="45">
+        <f t="shared" si="1"/>
+        <v>1.1852179246511625</v>
+      </c>
+      <c r="T15" s="40">
+        <f t="shared" si="1"/>
+        <v>9.1682158119817905E-2</v>
+      </c>
+      <c r="U15" s="40">
+        <f t="shared" si="1"/>
+        <v>3.2817337461300312E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="F16" s="40">
-        <f t="shared" ref="F16:L16" si="2">IFERROR(QUARTILE(F5:F12,1),"")</f>
+        <f t="shared" ref="F16:U16" si="2">IFERROR(QUARTILE(F5:F12,1),"")</f>
         <v>-1.6427970737561273E-2</v>
       </c>
       <c r="G16" s="40">
         <f t="shared" si="2"/>
-        <v>8.818040311955469E-2</v>
-      </c>
-      <c r="H16" s="50">
+        <v>8.7905510370431234E-2</v>
+      </c>
+      <c r="H16" s="51">
         <f t="shared" si="2"/>
-        <v>0.57936049701918968</v>
-      </c>
-      <c r="I16" s="50">
+        <v>0.64090595111563364</v>
+      </c>
+      <c r="I16" s="51">
         <f t="shared" si="2"/>
-        <v>7.7139868487134748</v>
-      </c>
-      <c r="J16" s="50">
+        <v>7.5049134589130704</v>
+      </c>
+      <c r="J16" s="51">
         <f t="shared" si="2"/>
-        <v>9.8324567597109223</v>
-      </c>
-      <c r="K16" s="50">
+        <v>9.3474784321695985</v>
+      </c>
+      <c r="K16" s="51">
         <f t="shared" si="2"/>
-        <v>11.969764250000001</v>
-      </c>
-      <c r="L16" s="50">
+        <v>11.949762249999999</v>
+      </c>
+      <c r="L16" s="51">
         <f t="shared" si="2"/>
-        <v>8.9798682500000009</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+        <v>10.59672002526834</v>
+      </c>
+      <c r="M16" s="51">
+        <f t="shared" si="2"/>
+        <v>0.60345186946787077</v>
+      </c>
+      <c r="N16" s="51">
+        <f t="shared" si="2"/>
+        <v>7.2708224734852429</v>
+      </c>
+      <c r="O16" s="51">
+        <f t="shared" si="2"/>
+        <v>11.054756908509216</v>
+      </c>
+      <c r="P16" s="51">
+        <f t="shared" si="2"/>
+        <v>10.437094129686699</v>
+      </c>
+      <c r="Q16" s="40">
+        <f t="shared" si="2"/>
+        <v>3.7325273620589572E-2</v>
+      </c>
+      <c r="R16" s="40">
+        <f t="shared" si="2"/>
+        <v>7.533408977548478E-2</v>
+      </c>
+      <c r="S16" s="45">
+        <f t="shared" si="2"/>
+        <v>0.79109234760766922</v>
+      </c>
+      <c r="T16" s="40">
+        <f t="shared" si="2"/>
+        <v>4.6978429888798606E-2</v>
+      </c>
+      <c r="U16" s="40">
+        <f t="shared" si="2"/>
+        <v>2.9476832274373581E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="F17" s="40">
-        <f t="shared" ref="F17:L17" si="3">IFERROR(QUARTILE(F5:F12,3),"")</f>
+        <f t="shared" ref="F17:U17" si="3">IFERROR(QUARTILE(F5:F12,3),"")</f>
         <v>7.5431165721922377E-2</v>
       </c>
       <c r="G17" s="40">
         <f t="shared" si="3"/>
-        <v>0.16979173013297574</v>
-      </c>
-      <c r="H17" s="50">
+        <v>0.16709840986225058</v>
+      </c>
+      <c r="H17" s="51">
         <f t="shared" si="3"/>
-        <v>1.5103733204205134</v>
-      </c>
-      <c r="I17" s="50">
+        <v>1.5047595918246093</v>
+      </c>
+      <c r="I17" s="51">
         <f t="shared" si="3"/>
-        <v>9.9081147421643045</v>
-      </c>
-      <c r="J17" s="50">
+        <v>9.4531595245101094</v>
+      </c>
+      <c r="J17" s="51">
         <f t="shared" si="3"/>
-        <v>25.211330047350117</v>
-      </c>
-      <c r="K17" s="50">
+        <v>11.737318789373175</v>
+      </c>
+      <c r="K17" s="51">
         <f t="shared" si="3"/>
-        <v>16.435001499999998</v>
-      </c>
-      <c r="L17" s="50">
+        <v>16.839440500000002</v>
+      </c>
+      <c r="L17" s="51">
         <f t="shared" si="3"/>
-        <v>13.428386249999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14.553044729867349</v>
+      </c>
+      <c r="M17" s="51">
+        <f t="shared" si="3"/>
+        <v>1.3748551163571268</v>
+      </c>
+      <c r="N17" s="51">
+        <f t="shared" si="3"/>
+        <v>8.9578674619955869</v>
+      </c>
+      <c r="O17" s="51">
+        <f t="shared" si="3"/>
+        <v>15.662227021564037</v>
+      </c>
+      <c r="P17" s="51">
+        <f t="shared" si="3"/>
+        <v>13.687658380264304</v>
+      </c>
+      <c r="Q17" s="40">
+        <f t="shared" si="3"/>
+        <v>5.5534785323032132E-2</v>
+      </c>
+      <c r="R17" s="40">
+        <f t="shared" si="3"/>
+        <v>0.12316718913487429</v>
+      </c>
+      <c r="S17" s="45">
+        <f t="shared" si="3"/>
+        <v>1.887451874658534</v>
+      </c>
+      <c r="T17" s="40">
+        <f t="shared" si="3"/>
+        <v>0.11008547572927598</v>
+      </c>
+      <c r="U17" s="40">
+        <f t="shared" si="3"/>
+        <v>3.9528890079405951E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="B21" s="28">
+        <v>222</v>
+      </c>
+      <c r="B21" s="29">
         <f>(Inputs!$B$5*Inputs!$B$6)*Inputs!$B$7</f>
-        <v>4846.8905121999996</v>
+        <v>4852.0086647999997</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E21" s="29">
+        <v>180</v>
+      </c>
+      <c r="E21" s="30">
         <f>IF(B23&lt;=0,"n.m.",B22/B23)</f>
-        <v>1.0906524586929112</v>
-      </c>
-      <c r="F21" s="29">
+        <v>1.2090711248158605</v>
+      </c>
+      <c r="F21" s="30">
         <f>H15</f>
-        <v>1.2157433254045971</v>
+        <v>1.2069209897800239</v>
       </c>
       <c r="G21" s="41">
         <f>IF(B23&lt;=0,"",(H15*B23-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>52.131006107002335</v>
-      </c>
-      <c r="H21" s="34">
+        <v>47.318481875573298</v>
+      </c>
+      <c r="H21" s="35">
         <f>IF(G21="","",G21/Inputs!$B$5-1)</f>
-        <v>0.10097161788811682</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+        <v>-1.7197916545717007E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B22" s="28">
+        <v>141</v>
+      </c>
+      <c r="B22" s="29">
         <f>B21+Inputs!$B$8+Inputs!$B$9</f>
-        <v>4267.0065121999996</v>
+        <v>4692.2756647999995</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E22" s="29">
+        <v>181</v>
+      </c>
+      <c r="E22" s="30">
         <f>IF(B24&lt;=0,"n.m.",B22/B24)</f>
-        <v>8.1275372110804316</v>
-      </c>
-      <c r="F22" s="29">
+        <v>9.5143159715003502</v>
+      </c>
+      <c r="F22" s="30">
         <f>I15</f>
-        <v>8.4924439717599984</v>
+        <v>8.9872662844646616</v>
       </c>
       <c r="G22" s="41">
         <f>IF(B24&lt;=0,"",(I15*B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>49.221556845791177</v>
-      </c>
-      <c r="H22" s="34">
+        <v>44.860698426398507</v>
+      </c>
+      <c r="H22" s="35">
         <f>IF(G22="","",G22/Inputs!$B$5-1)</f>
-        <v>3.9526015750605659E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+        <v>-5.3571763156149643E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B23" s="31">
-        <f>Historicals!E5</f>
-        <v>3912.3429999999998</v>
+        <v>223</v>
+      </c>
+      <c r="B23" s="18">
+        <v>3880.893</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" s="29">
+        <v>182</v>
+      </c>
+      <c r="E23" s="30">
         <f>IF(B25&lt;=0,"n.m.",B22/B25)</f>
-        <v>8.830266934764639</v>
-      </c>
-      <c r="F23" s="29">
+        <v>10.447709335000727</v>
+      </c>
+      <c r="F23" s="30">
         <f>J15</f>
-        <v>10.74775198806914</v>
+        <v>10.177790463860751</v>
       </c>
       <c r="G23" s="41">
         <f>IF(B25&lt;=0,"",(J15*B25-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>56.401868467765198</v>
-      </c>
-      <c r="H23" s="34">
+        <v>46.215725277638285</v>
+      </c>
+      <c r="H23" s="35">
         <f>IF(G23="","",G23/Inputs!$B$5-1)</f>
-        <v>0.19116934462017299</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+        <v>-2.4984698784002446E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="B24" s="31">
-        <f>Historicals!E9</f>
-        <v>525.00608750000004</v>
+        <v>224</v>
+      </c>
+      <c r="B24" s="18">
+        <v>493.18055852417268</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E24" s="29">
+        <v>183</v>
+      </c>
+      <c r="E24" s="30">
         <f>IF(B26&lt;=0,"n.m.",(Inputs!$B$5*Inputs!$B$6)/B26)</f>
-        <v>13.684971098265896</v>
-      </c>
-      <c r="F24" s="29">
+        <v>14.766355140186915</v>
+      </c>
+      <c r="F24" s="30">
         <f>K15</f>
-        <v>15.236610000000001</v>
+        <v>14.740622500000001</v>
       </c>
       <c r="G24" s="41">
         <f>IF(B26&lt;=0,"",K15*B26/Inputs!$B$6)</f>
-        <v>52.718670600000003</v>
-      </c>
-      <c r="H24" s="34">
+        <v>47.317398224999998</v>
+      </c>
+      <c r="H24" s="35">
         <f>IF(G24="","",G24/Inputs!$B$5-1)</f>
-        <v>0.11338269482576568</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+        <v>-1.742653481012657E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="B25" s="31">
-        <f>Historicals!E14</f>
-        <v>483.22508749999997</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+      <c r="B25" s="18">
+        <v>449.12004290552682</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="B26" s="4">
-        <f>Historicals!E23</f>
-        <v>3.46</v>
+        <v>226</v>
+      </c>
+      <c r="B26" s="24">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" s="24">
+        <v>7.0920671452332256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A32" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B32" s="24">
+        <v>92.987254701420341</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B33" s="24">
+        <v>-14.032292373299169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B34" s="24">
+        <v>0.3758819957643329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B35" s="24">
+        <v>3.6755187206814082</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B36" s="22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B37" s="19">
+        <v>7.7636014568835954E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B38" s="35">
+        <f>IF(B23&gt;0,B24/B23,0)</f>
+        <v>0.1270791435177864</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B39" s="51">
+        <f>B31+B32*B37+B33*B38</f>
+        <v>12.528015309558731</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B40" s="45">
+        <f>IF(B24&lt;=0,"",(B39*B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>61.91986721505296</v>
       </c>
     </row>
   </sheetData>
@@ -6219,7 +6867,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6228,134 +6876,151 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>213</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="B5" s="23">
+        <v>246</v>
+      </c>
+      <c r="B5" s="24">
         <v>42.15</v>
       </c>
-      <c r="C5" s="23">
-        <v>67.8</v>
+      <c r="C5" s="24">
+        <v>67</v>
       </c>
       <c r="D5" s="41">
-        <f>IFERROR(C5-B5,"")</f>
-        <v>25.65</v>
+        <f t="shared" ref="D5:D10" si="0">IFERROR(C5-B5,"")</f>
+        <v>24.85</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="B6" s="41">
         <f>MIN(DCF!D40:F42)</f>
-        <v>68.860386900919735</v>
+        <v>66.907100450329892</v>
       </c>
       <c r="C6" s="41">
         <f>MAX(DCF!D40:F42)</f>
-        <v>84.511377333785276</v>
+        <v>82.982999622296575</v>
       </c>
       <c r="D6" s="41">
-        <f>IFERROR(C6-B6,"")</f>
-        <v>15.650990432865541</v>
+        <f t="shared" si="0"/>
+        <v>16.075899171966682</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="B7" s="41">
         <f>(Peers!I16*Peers!B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>45.228956776997194</v>
+        <v>37.718789503680775</v>
       </c>
       <c r="C7" s="41">
         <f>(Peers!I17*Peers!B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>56.482338522739177</v>
+        <v>47.105351002195583</v>
       </c>
       <c r="D7" s="41">
-        <f>IFERROR(C7-B7,"")</f>
-        <v>11.253381745741983</v>
+        <f t="shared" si="0"/>
+        <v>9.3865614985148085</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="B8" s="41">
         <f>(Peers!J16*Peers!B25-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>52.081035821902582</v>
+        <v>42.572713780695963</v>
       </c>
       <c r="C8" s="41">
         <f>(Peers!J17*Peers!B25-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>124.68005709835752</v>
+        <v>53.058188596009494</v>
       </c>
       <c r="D8" s="41">
-        <f>IFERROR(C8-B8,"")</f>
-        <v>72.599021276454948</v>
+        <f t="shared" si="0"/>
+        <v>10.48547481531353</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="B9" s="41">
         <f>Peers!K16*Peers!B26/Inputs!$B$6</f>
-        <v>41.415384305000003</v>
+        <v>38.358736822499999</v>
       </c>
       <c r="C9" s="41">
         <f>Peers!K17*Peers!B26/Inputs!$B$6</f>
-        <v>56.865105189999994</v>
+        <v>54.054604005000009</v>
       </c>
       <c r="D9" s="41">
-        <f>IFERROR(C9-B9,"")</f>
-        <v>15.449720884999991</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="4">
-        <f>Inputs!$B$5</f>
-        <v>47.35</v>
+        <f t="shared" si="0"/>
+        <v>15.69586718250001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="B10" s="41">
+        <f>((Peers!$B$39-Peers!$B$35)*Peers!$B$24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
+        <v>44.211384123598144</v>
+      </c>
+      <c r="C10" s="41">
+        <f>((Peers!$B$39+Peers!$B$35)*Peers!$B$24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
+        <v>79.62835030650777</v>
+      </c>
+      <c r="D10" s="41">
+        <f t="shared" si="0"/>
+        <v>35.416966182909626</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="51">
-        <f>DCF!$B$30</f>
-        <v>78.5</v>
+        <v>146</v>
+      </c>
+      <c r="B12" s="4">
+        <f>Inputs!$B$5</f>
+        <v>47.4</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="52">
+        <f>DCF!$B$30</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="52" t="str">
+      <c r="B14" s="53" t="str">
         <f>DCF!$B$33</f>
         <v>BUY</v>
       </c>
